--- a/Multicancer detection/00_Data/Train.xlsx
+++ b/Multicancer detection/00_Data/Train.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30106"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSoft\Pycharm\PythonProject\PythonProject\Data analysis\ML\A_Code for manuscript\Source code for submission\Multicancer detection\03_Ensemble\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSoft\Pycharm\PythonProject\PythonProject\Archive\01_tri_cancer_screening\Source code for submission\Multicancer detection\00_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F483C89E-F225-4A15-BCAC-027FFDB01A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DA150D-29EE-452E-95C3-507BB9B80A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30600" yWindow="8004" windowWidth="17400" windowHeight="15036" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,45 +61,43 @@
   </si>
   <si>
     <t>dwl(9,1)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dwl(8,3)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dwl(7,5)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dwl(7,3)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dwl(6,5)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dwl(6,4)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -111,7 +109,18 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -123,28 +132,10 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -153,24 +144,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -449,6378 +441,6401 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{96D7089E-891B-420A-BA40-FD658B8524F1}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;d3b6b797-be8f-4921-b19f-823d548ae19a&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N155"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="13" width="17.6640625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="15" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="17.6640625" style="6" customWidth="1"/>
+    <col min="2" max="13" width="17.6640625" style="7" customWidth="1"/>
+    <col min="14" max="14" width="15" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="5">
         <v>-0.37197000000000002</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>1.42896</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="5">
         <v>-0.16944999999999999</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="5">
         <v>-0.52700000000000002</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="5">
         <v>0.84772000000000003</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="5">
         <v>0.70457999999999998</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>-0.56100000000000005</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="5">
         <v>-0.56140000000000001</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="5">
         <v>0.38052000000000002</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="5">
         <v>1.5044999999999999</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="5">
         <v>6.368E-2</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="5">
         <v>-1.8450000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="5">
         <v>-0.44629000000000002</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>2.0515500000000002</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="5">
         <v>-0.42369000000000001</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="5">
         <v>-0.54649999999999999</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="5">
         <v>1.04965</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="5">
         <v>0.76270000000000004</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>-0.44409999999999999</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="5">
         <v>-0.69055</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="5">
         <v>0.26937</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="5">
         <v>1.3174999999999999</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="5">
         <v>-7.109E-2</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="5">
         <v>-4.7890000000000002E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <v>-0.56686000000000003</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>2.79359</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>-0.43031999999999998</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>-0.68489</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <v>0.74746000000000001</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>0.74353999999999998</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>-0.48276000000000002</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="5">
         <v>-1.21275</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>0.28722999999999999</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="5">
         <v>1.5077499999999999</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="5">
         <v>0.18321999999999999</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="5">
         <v>-0.14334</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>-0.73014999999999997</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>2.3098299999999998</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>-0.53083000000000002</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>-0.69628000000000001</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <v>0.87639</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>0.77078000000000002</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>-0.77815999999999996</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="5">
         <v>-0.91935</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="5">
         <v>0.28375</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="5">
         <v>1.5107699999999999</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="5">
         <v>1.38E-2</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="5">
         <v>-0.12146</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <v>-0.33579999999999999</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>2.87107</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>-0.59296000000000004</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>-0.60918000000000005</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>1.0103</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>0.97250000000000003</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>-1.11442</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="5">
         <v>-1.3658999999999999</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <v>0.19994999999999999</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="5">
         <v>1.3235600000000001</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="5">
         <v>-5.7590000000000002E-2</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="5">
         <v>-0.15820999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="5">
         <v>-0.74251999999999996</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>2.0079199999999999</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>-6.8650000000000003E-2</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>-1.1051200000000001</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>0.44535999999999998</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="5">
         <v>0.59736</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>-0.71906999999999999</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="5">
         <v>-1.9811700000000001</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="5">
         <v>0.33363999999999999</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="5">
         <v>1.7033400000000001</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="5">
         <v>-2.2440000000000002E-2</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7" s="5">
         <v>-9.2149999999999996E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>-0.53785000000000005</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>1.71184</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>-0.49492999999999998</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>-0.19797000000000001</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>0.64395999999999998</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>1.0943499999999999</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>-1.13121</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="5">
         <v>-1.29583</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="5">
         <v>0.28292</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="5">
         <v>1.1495899999999999</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="5">
         <v>-7.4520000000000003E-2</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="5">
         <v>-0.16993</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <v>-0.66237999999999997</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>1.74597</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>0.27583999999999997</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>-1.31497</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>0.39806999999999998</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="5">
         <v>0.78468000000000004</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>-0.81855</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="5">
         <v>-1.18025</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="5">
         <v>0.30591000000000002</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="5">
         <v>1.5929500000000001</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="5">
         <v>-0.1288</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9" s="5">
         <v>-0.13194</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>-0.13996</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>2.1409400000000001</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>0.25968000000000002</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>-0.59492</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <v>0.34731000000000001</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="5">
         <v>0.93189999999999995</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>-0.69162999999999997</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="5">
         <v>-1.50665</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="5">
         <v>0.42647000000000002</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="5">
         <v>1.6754800000000001</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="5">
         <v>-3.1739999999999997E-2</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10" s="5">
         <v>-6.5750000000000003E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="5">
         <v>-0.26649</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>0.85355999999999999</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>0.46048</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>-0.52610000000000001</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>0.36</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>0.77698</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>-1.1673500000000001</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="5">
         <v>0.21657999999999999</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="5">
         <v>0.56637000000000004</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="5">
         <v>1.6784600000000001</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="5">
         <v>-2.8268800000000001E-4</v>
       </c>
-      <c r="M11" s="4">
+      <c r="M11" s="5">
         <v>-1.8239999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="5">
         <v>-1.2994699999999999</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>-0.95459000000000005</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>-0.67608999999999997</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>-1.71357</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>-0.33776</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <v>-0.43353000000000003</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>-0.45828999999999998</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="5">
         <v>-1.7101</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>0.18228</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="5">
         <v>2.9533800000000001</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="5">
         <v>-3.2199999999999999E-2</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M12" s="5">
         <v>-3.2489999999999998E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="5">
         <v>-1.65123</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>-1.5981700000000001</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>-8.0400000000000003E-3</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>-1.9446399999999999</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <v>-0.38640999999999998</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="5">
         <v>-0.26496999999999998</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>-0.51422000000000001</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="5">
         <v>-1.5154799999999999</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="5">
         <v>0.27060000000000001</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="5">
         <v>2.1280899999999998</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="5">
         <v>7.9640000000000002E-2</v>
       </c>
-      <c r="M13" s="4">
+      <c r="M13" s="5">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="5">
         <v>-1.04538</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>-5.8349999999999999E-2</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>-0.81257000000000001</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>-1.69994</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="5">
         <v>0.83172000000000001</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <v>0.29249999999999998</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>-0.61443000000000003</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="5">
         <v>-1.7766500000000001</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="5">
         <v>0.23738000000000001</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="5">
         <v>2.36707</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="5">
         <v>-6.6180000000000003E-2</v>
       </c>
-      <c r="M14" s="4">
+      <c r="M14" s="5">
         <v>-8.9200000000000002E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="5">
         <v>-1.3448100000000001</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>-1.13161</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>-0.91737999999999997</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <v>-1.70482</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="5">
         <v>-0.73451</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="5">
         <v>-0.32629000000000002</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>7.9810000000000006E-2</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="5">
         <v>-2.09477</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="5">
         <v>0.38923999999999997</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="5">
         <v>2.36435</v>
       </c>
-      <c r="L15" s="4">
+      <c r="L15" s="5">
         <v>-0.12371</v>
       </c>
-      <c r="M15" s="4">
+      <c r="M15" s="5">
         <v>0.21199000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="5">
         <v>-0.70243</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>0.62751000000000001</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>-0.44296000000000002</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>-1.4558599999999999</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <v>0.54937999999999998</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <v>0.58689000000000002</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>-0.40277000000000002</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="5">
         <v>-1.7512399999999999</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="5">
         <v>0.41675000000000001</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="5">
         <v>2.1371600000000002</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L16" s="5">
         <v>-3.9570000000000001E-2</v>
       </c>
-      <c r="M16" s="4">
+      <c r="M16" s="5">
         <v>1.35E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="5">
         <v>-0.93520999999999999</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>0.49830999999999998</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <v>-8.2040000000000002E-2</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <v>-1.68041</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="5">
         <v>-0.37885999999999997</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="5">
         <v>-0.22488</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <v>-0.10553999999999999</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="5">
         <v>-1.7885599999999999</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="5">
         <v>0.50431999999999999</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="5">
         <v>1.9971300000000001</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L17" s="5">
         <v>0.18429999999999999</v>
       </c>
-      <c r="M17" s="4">
+      <c r="M17" s="5">
         <v>3.2289999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="5">
         <v>-1.30525</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <v>0.22944000000000001</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
         <v>-0.83274000000000004</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <v>-2.0259499999999999</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="5">
         <v>0.22789000000000001</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="5">
         <v>-3.397E-2</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>-0.67196999999999996</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="5">
         <v>-1.81033</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="5">
         <v>0.43114000000000002</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="5">
         <v>2.3549899999999999</v>
       </c>
-      <c r="L18" s="4">
+      <c r="L18" s="5">
         <v>1.9869999999999999E-2</v>
       </c>
-      <c r="M18" s="4">
+      <c r="M18" s="5">
         <v>-0.11183999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="5">
         <v>-0.63944999999999996</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <v>1.1156999999999999</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="5">
         <v>-0.37375999999999998</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <v>-1.1480600000000001</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="5">
         <v>0.26618000000000003</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="5">
         <v>0.67571000000000003</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>-0.52639999999999998</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="5">
         <v>-1.99559</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="5">
         <v>0.27921000000000001</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="5">
         <v>1.9729099999999999</v>
       </c>
-      <c r="L19" s="4">
+      <c r="L19" s="5">
         <v>6.9550000000000001E-2</v>
       </c>
-      <c r="M19" s="4">
+      <c r="M19" s="5">
         <v>-5.91E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="5">
         <v>-1.1816199999999999</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>-0.37408999999999998</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>-0.35843999999999998</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <v>-1.5754900000000001</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="5">
         <v>-0.63887000000000005</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="5">
         <v>-0.20804</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>-1.5779999999999999E-2</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="5">
         <v>-2.1646100000000001</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="5">
         <v>0.34181</v>
       </c>
-      <c r="K20" s="4">
+      <c r="K20" s="5">
         <v>2.02658</v>
       </c>
-      <c r="L20" s="4">
+      <c r="L20" s="5">
         <v>-0.12214</v>
       </c>
-      <c r="M20" s="4">
+      <c r="M20" s="5">
         <v>-3.5899999999999999E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="5">
         <v>-0.87936000000000003</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>-9.8280000000000006E-2</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <v>-0.46217000000000003</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="5">
         <v>-1.9972399999999999</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="5">
         <v>0.20882999999999999</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="5">
         <v>0.58726999999999996</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>-0.49909999999999999</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="5">
         <v>-2.2115100000000001</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="5">
         <v>0.38231999999999999</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="5">
         <v>2.0796199999999998</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L21" s="5">
         <v>1.508E-2</v>
       </c>
-      <c r="M21" s="4">
+      <c r="M21" s="5">
         <v>-8.6199999999999992E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="5">
         <v>-1.19679</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>-0.16513</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="5">
         <v>-0.79346000000000005</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="5">
         <v>-1.0968800000000001</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="5">
         <v>0.73424</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="5">
         <v>0.13245000000000001</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>-0.57028000000000001</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="5">
         <v>-1.75091</v>
       </c>
-      <c r="J22" s="4">
+      <c r="J22" s="5">
         <v>0.15409</v>
       </c>
-      <c r="K22" s="4">
+      <c r="K22" s="5">
         <v>1.83816</v>
       </c>
-      <c r="L22" s="4">
+      <c r="L22" s="5">
         <v>-8.4600000000000005E-3</v>
       </c>
-      <c r="M22" s="4">
+      <c r="M22" s="5">
         <v>-0.10792</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="5">
         <v>-0.76726000000000005</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>0.88031999999999999</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <v>-1.0763</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <v>-1.1486499999999999</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="5">
         <v>0.64661999999999997</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="5">
         <v>0.47055999999999998</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>-0.64344000000000001</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="5">
         <v>-1.8041100000000001</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="5">
         <v>0.17138999999999999</v>
       </c>
-      <c r="K23" s="4">
+      <c r="K23" s="5">
         <v>1.56626</v>
       </c>
-      <c r="L23" s="4">
+      <c r="L23" s="5">
         <v>4.8480000000000002E-2</v>
       </c>
-      <c r="M23" s="4">
+      <c r="M23" s="5">
         <v>1.405E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="5">
         <v>-0.75483</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
         <v>2.2669299999999999</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="5">
         <v>-0.43713999999999997</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="5">
         <v>-1.3630500000000001</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="5">
         <v>0.85299999999999998</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="5">
         <v>0.66417999999999999</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>-0.86224999999999996</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="5">
         <v>-1.1436200000000001</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="5">
         <v>0.26766000000000001</v>
       </c>
-      <c r="K24" s="4">
+      <c r="K24" s="5">
         <v>1.93181</v>
       </c>
-      <c r="L24" s="4">
+      <c r="L24" s="5">
         <v>4.3099999999999999E-2</v>
       </c>
-      <c r="M24" s="4">
+      <c r="M24" s="5">
         <v>-8.5059999999999997E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="5">
         <v>-0.80156000000000005</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <v>0.69986999999999999</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="5">
         <v>-0.58457999999999999</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="5">
         <v>-1.0596099999999999</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="5">
         <v>0.56796000000000002</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="5">
         <v>0.21578</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>-0.83945999999999998</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I25" s="5">
         <v>-0.22070000000000001</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J25" s="5">
         <v>0.29352</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K25" s="5">
         <v>1.62913</v>
       </c>
-      <c r="L25" s="4">
+      <c r="L25" s="5">
         <v>-2.393E-2</v>
       </c>
-      <c r="M25" s="4">
+      <c r="M25" s="5">
         <v>-0.10494000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="5">
         <v>-0.48476000000000002</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="5">
         <v>1.7476400000000001</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="5">
         <v>-0.37347000000000002</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="5">
         <v>-0.97279000000000004</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="5">
         <v>0.56725000000000003</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="5">
         <v>0.48265000000000002</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="5">
         <v>-0.70570999999999995</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I26" s="5">
         <v>-1.27284</v>
       </c>
-      <c r="J26" s="4">
+      <c r="J26" s="5">
         <v>0.20910999999999999</v>
       </c>
-      <c r="K26" s="4">
+      <c r="K26" s="5">
         <v>0.63888</v>
       </c>
-      <c r="L26" s="4">
+      <c r="L26" s="5">
         <v>-8.7540000000000007E-2</v>
       </c>
-      <c r="M26" s="4">
+      <c r="M26" s="5">
         <v>-9.221E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="5">
         <v>-0.85575999999999997</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
         <v>5.7709999999999997E-2</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="5">
         <v>-0.60287999999999997</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="5">
         <v>-1.68058</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="5">
         <v>0.48463000000000001</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="5">
         <v>0.43934000000000001</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="5">
         <v>-0.39126</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="5">
         <v>-1.68011</v>
       </c>
-      <c r="J27" s="4">
+      <c r="J27" s="5">
         <v>0.22327</v>
       </c>
-      <c r="K27" s="4">
+      <c r="K27" s="5">
         <v>2.1492399999999998</v>
       </c>
-      <c r="L27" s="4">
+      <c r="L27" s="5">
         <v>-5.1729999999999998E-2</v>
       </c>
-      <c r="M27" s="4">
+      <c r="M27" s="5">
         <v>-2.31E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="5">
         <v>-0.70392999999999994</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <v>2.1201400000000001</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="5">
         <v>-0.38995999999999997</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="5">
         <v>-1.14635</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="5">
         <v>0.54876000000000003</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28" s="5">
         <v>0.85624999999999996</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="5">
         <v>-0.77576000000000001</v>
       </c>
-      <c r="I28" s="4">
+      <c r="I28" s="5">
         <v>-1.9777400000000001</v>
       </c>
-      <c r="J28" s="4">
+      <c r="J28" s="5">
         <v>0.43817</v>
       </c>
-      <c r="K28" s="4">
+      <c r="K28" s="5">
         <v>1.73468</v>
       </c>
-      <c r="L28" s="4">
+      <c r="L28" s="5">
         <v>-0.17888999999999999</v>
       </c>
-      <c r="M28" s="4">
+      <c r="M28" s="5">
         <v>1.106E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="5">
         <v>-0.96230000000000004</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <v>-0.40383000000000002</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="5">
         <v>-0.35148000000000001</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="5">
         <v>-1.4232100000000001</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="5">
         <v>-5.1249999999999997E-2</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="5">
         <v>-2.1129999999999999E-2</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="5">
         <v>-8.2849999999999993E-2</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29" s="5">
         <v>-1.70486</v>
       </c>
-      <c r="J29" s="4">
+      <c r="J29" s="5">
         <v>0.40827999999999998</v>
       </c>
-      <c r="K29" s="4">
+      <c r="K29" s="5">
         <v>1.8611500000000001</v>
       </c>
-      <c r="L29" s="4">
+      <c r="L29" s="5">
         <v>-0.152</v>
       </c>
-      <c r="M29" s="4">
+      <c r="M29" s="5">
         <v>4.4839999999999998E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="5">
         <v>-0.75885999999999998</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>-0.13866000000000001</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="5">
         <v>-0.16508999999999999</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="5">
         <v>-1.70438</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="5">
         <v>0.49141000000000001</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="5">
         <v>0.36132999999999998</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="5">
         <v>-0.41169</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="5">
         <v>-1.70777</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="5">
         <v>0.27944000000000002</v>
       </c>
-      <c r="K30" s="4">
+      <c r="K30" s="5">
         <v>2.2883599999999999</v>
       </c>
-      <c r="L30" s="4">
+      <c r="L30" s="5">
         <v>-3.0190000000000002E-2</v>
       </c>
-      <c r="M30" s="4">
+      <c r="M30" s="5">
         <v>7.8839999999999993E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="5">
         <v>-0.79607000000000006</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="5">
         <v>8.9580000000000007E-2</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="5">
         <v>0.13569999999999999</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="5">
         <v>-1.4863500000000001</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="5">
         <v>-0.36867</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="5">
         <v>0.17424000000000001</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="5">
         <v>-0.42759000000000003</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I31" s="5">
         <v>-1.8033699999999999</v>
       </c>
-      <c r="J31" s="4">
+      <c r="J31" s="5">
         <v>0.35416999999999998</v>
       </c>
-      <c r="K31" s="4">
+      <c r="K31" s="5">
         <v>2.4832800000000002</v>
       </c>
-      <c r="L31" s="4">
+      <c r="L31" s="5">
         <v>-2.5159999999999998E-2</v>
       </c>
-      <c r="M31" s="4">
+      <c r="M31" s="5">
         <v>7.1700000000000002E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="5">
         <v>-0.39208999999999999</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="5">
         <v>1.9411499999999999</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="5">
         <v>-0.29826999999999998</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="5">
         <v>-0.75495000000000001</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="5">
         <v>0.54696</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="5">
         <v>0.35596</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="5">
         <v>-0.75932999999999995</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32" s="5">
         <v>-0.56149000000000004</v>
       </c>
-      <c r="J32" s="4">
+      <c r="J32" s="5">
         <v>0.23179</v>
       </c>
-      <c r="K32" s="4">
+      <c r="K32" s="5">
         <v>1.68075</v>
       </c>
-      <c r="L32" s="4">
+      <c r="L32" s="5">
         <v>1.7010000000000001E-2</v>
       </c>
-      <c r="M32" s="4">
+      <c r="M32" s="5">
         <v>-0.13963</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="5">
         <v>-0.56896000000000002</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="5">
         <v>1.9326300000000001</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="5">
         <v>-0.60541999999999996</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="5">
         <v>-0.81647999999999998</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="5">
         <v>0.79117999999999999</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33" s="5">
         <v>0.50422</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H33" s="5">
         <v>-0.96223999999999998</v>
       </c>
-      <c r="I33" s="4">
+      <c r="I33" s="5">
         <v>-0.63665000000000005</v>
       </c>
-      <c r="J33" s="4">
+      <c r="J33" s="5">
         <v>0.27095999999999998</v>
       </c>
-      <c r="K33" s="4">
+      <c r="K33" s="5">
         <v>1.89764</v>
       </c>
-      <c r="L33" s="4">
+      <c r="L33" s="5">
         <v>-4.1759999999999999E-2</v>
       </c>
-      <c r="M33" s="4">
+      <c r="M33" s="5">
         <v>-0.14398</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="5">
         <v>-0.42202000000000001</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="5">
         <v>2.6092</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="5">
         <v>-0.23857999999999999</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="5">
         <v>-0.77546000000000004</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="5">
         <v>0.29108000000000001</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="5">
         <v>0.57613999999999999</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="5">
         <v>-0.81196999999999997</v>
       </c>
-      <c r="I34" s="4">
+      <c r="I34" s="5">
         <v>-1.0340100000000001</v>
       </c>
-      <c r="J34" s="4">
+      <c r="J34" s="5">
         <v>0.29370000000000002</v>
       </c>
-      <c r="K34" s="4">
+      <c r="K34" s="5">
         <v>1.0287599999999999</v>
       </c>
-      <c r="L34" s="4">
+      <c r="L34" s="5">
         <v>-4.7199999999999999E-2</v>
       </c>
-      <c r="M34" s="4">
+      <c r="M34" s="5">
         <v>-0.10221</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="5">
         <v>-0.70767000000000002</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="5">
         <v>2.4695200000000002</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="5">
         <v>-0.59891000000000005</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="5">
         <v>-0.52212000000000003</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="5">
         <v>0.75675000000000003</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="5">
         <v>0.77195000000000003</v>
       </c>
-      <c r="H35" s="6">
+      <c r="H35" s="5">
         <v>-1.02206</v>
       </c>
-      <c r="I35" s="4">
+      <c r="I35" s="5">
         <v>-0.96457999999999999</v>
       </c>
-      <c r="J35" s="4">
+      <c r="J35" s="5">
         <v>0.21429000000000001</v>
       </c>
-      <c r="K35" s="4">
+      <c r="K35" s="5">
         <v>1.39364</v>
       </c>
-      <c r="L35" s="4">
+      <c r="L35" s="5">
         <v>-3.3820000000000003E-2</v>
       </c>
-      <c r="M35" s="4">
+      <c r="M35" s="5">
         <v>-7.9149999999999998E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="5">
         <v>-0.66603999999999997</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="5">
         <v>1.77485</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="5">
         <v>0.12747</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="5">
         <v>-0.73858999999999997</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="5">
         <v>0.47387000000000001</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="5">
         <v>0.42149999999999999</v>
       </c>
-      <c r="H36" s="6">
+      <c r="H36" s="5">
         <v>-0.97909000000000002</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I36" s="5">
         <v>-0.45984999999999998</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J36" s="5">
         <v>0.30879000000000001</v>
       </c>
-      <c r="K36" s="4">
+      <c r="K36" s="5">
         <v>1.1935199999999999</v>
       </c>
-      <c r="L36" s="4">
+      <c r="L36" s="5">
         <v>3.15E-3</v>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="5">
         <v>5.9997900000000005E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="5">
         <v>-0.48704999999999998</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="5">
         <v>1.6738599999999999</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="5">
         <v>-0.42348000000000002</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="5">
         <v>-0.77519000000000005</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="5">
         <v>0.90698000000000001</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37" s="5">
         <v>0.96186000000000005</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37" s="5">
         <v>-0.99087999999999998</v>
       </c>
-      <c r="I37" s="4">
+      <c r="I37" s="5">
         <v>-0.97604999999999997</v>
       </c>
-      <c r="J37" s="4">
+      <c r="J37" s="5">
         <v>0.27794000000000002</v>
       </c>
-      <c r="K37" s="4">
+      <c r="K37" s="5">
         <v>1.5330699999999999</v>
       </c>
-      <c r="L37" s="4">
+      <c r="L37" s="5">
         <v>-2.4760000000000001E-2</v>
       </c>
-      <c r="M37" s="4">
+      <c r="M37" s="5">
         <v>-6.8440000000000001E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="5">
         <v>-2.9870000000000001E-2</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="5">
         <v>2.90055</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="5">
         <v>-0.49697999999999998</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="5">
         <v>-0.69964000000000004</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="5">
         <v>0.99134</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G38" s="5">
         <v>1.0642499999999999</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38" s="5">
         <v>-0.70130999999999999</v>
       </c>
-      <c r="I38" s="4">
+      <c r="I38" s="5">
         <v>-1.5623100000000001</v>
       </c>
-      <c r="J38" s="4">
+      <c r="J38" s="5">
         <v>0.33260000000000001</v>
       </c>
-      <c r="K38" s="4">
+      <c r="K38" s="5">
         <v>1.8492200000000001</v>
       </c>
-      <c r="L38" s="4">
+      <c r="L38" s="5">
         <v>7.4700000000000001E-3</v>
       </c>
-      <c r="M38" s="4">
+      <c r="M38" s="5">
         <v>-0.15862999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="5">
         <v>-0.29933999999999999</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="5">
         <v>1.6213599999999999</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="5">
         <v>-0.18296000000000001</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="5">
         <v>-0.4244</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="5">
         <v>0.96533000000000002</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="5">
         <v>0.74407999999999996</v>
       </c>
-      <c r="H39" s="6">
+      <c r="H39" s="5">
         <v>-0.96665000000000001</v>
       </c>
-      <c r="I39" s="4">
+      <c r="I39" s="5">
         <v>-0.70667000000000002</v>
       </c>
-      <c r="J39" s="4">
+      <c r="J39" s="5">
         <v>0.2959</v>
       </c>
-      <c r="K39" s="4">
+      <c r="K39" s="5">
         <v>1.119</v>
       </c>
-      <c r="L39" s="4">
+      <c r="L39" s="5">
         <v>-1.076E-2</v>
       </c>
-      <c r="M39" s="4">
+      <c r="M39" s="5">
         <v>-8.1949999999999995E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="5">
         <v>-0.61001000000000005</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="5">
         <v>2.2186699999999999</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="5">
         <v>0.51944999999999997</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="5">
         <v>-0.70750000000000002</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="5">
         <v>0.92044999999999999</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G40" s="5">
         <v>1.0392300000000001</v>
       </c>
-      <c r="H40" s="6">
+      <c r="H40" s="5">
         <v>-1.03199</v>
       </c>
-      <c r="I40" s="4">
+      <c r="I40" s="5">
         <v>-0.68991000000000002</v>
       </c>
-      <c r="J40" s="4">
+      <c r="J40" s="5">
         <v>0.36273</v>
       </c>
-      <c r="K40" s="4">
+      <c r="K40" s="5">
         <v>1.1753199999999999</v>
       </c>
-      <c r="L40" s="4">
+      <c r="L40" s="5">
         <v>-2.334E-2</v>
       </c>
-      <c r="M40" s="4">
+      <c r="M40" s="5">
         <v>-0.10718999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="5">
         <v>-5.7520000000000002E-2</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="5">
         <v>2.5375000000000001</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="5">
         <v>0.35310999999999998</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="5">
         <v>-0.88427999999999995</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="5">
         <v>0.52153000000000005</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41" s="5">
         <v>1.2176800000000001</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="5">
         <v>-0.73714999999999997</v>
       </c>
-      <c r="I41" s="4">
+      <c r="I41" s="5">
         <v>-1.0313600000000001</v>
       </c>
-      <c r="J41" s="4">
+      <c r="J41" s="5">
         <v>0.37636999999999998</v>
       </c>
-      <c r="K41" s="4">
+      <c r="K41" s="5">
         <v>1.30846</v>
       </c>
-      <c r="L41" s="4">
+      <c r="L41" s="5">
         <v>5.6340000000000001E-2</v>
       </c>
-      <c r="M41" s="4">
+      <c r="M41" s="5">
         <v>-6.4350000000000004E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="5">
         <v>-0.77781999999999996</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="5">
         <v>2.6031200000000001</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="5">
         <v>0.22061</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="5">
         <v>-0.53878999999999999</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="5">
         <v>0.29476000000000002</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G42" s="5">
         <v>0.54215999999999998</v>
       </c>
-      <c r="H42" s="6">
+      <c r="H42" s="5">
         <v>-1.0287500000000001</v>
       </c>
-      <c r="I42" s="4">
+      <c r="I42" s="5">
         <v>-0.35675000000000001</v>
       </c>
-      <c r="J42" s="4">
+      <c r="J42" s="5">
         <v>0.17155000000000001</v>
       </c>
-      <c r="K42" s="4">
+      <c r="K42" s="5">
         <v>1.6043400000000001</v>
       </c>
-      <c r="L42" s="4">
+      <c r="L42" s="5">
         <v>-3.5639999999999998E-2</v>
       </c>
-      <c r="M42" s="4">
+      <c r="M42" s="5">
         <v>-0.17857000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="5">
         <v>-0.87292000000000003</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="5">
         <v>1.31077</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="5">
         <v>0.27660000000000001</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="5">
         <v>-0.22292000000000001</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="5">
         <v>0.10359</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G43" s="5">
         <v>0.69098000000000004</v>
       </c>
-      <c r="H43" s="6">
+      <c r="H43" s="5">
         <v>-1.43384</v>
       </c>
-      <c r="I43" s="4">
+      <c r="I43" s="5">
         <v>-0.58723000000000003</v>
       </c>
-      <c r="J43" s="4">
+      <c r="J43" s="5">
         <v>0.16150999999999999</v>
       </c>
-      <c r="K43" s="4">
+      <c r="K43" s="5">
         <v>1.16896</v>
       </c>
-      <c r="L43" s="4">
+      <c r="L43" s="5">
         <v>-0.12797</v>
       </c>
-      <c r="M43" s="4">
+      <c r="M43" s="5">
         <v>-9.3500000000000007E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="5">
         <v>-0.56891999999999998</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="5">
         <v>1.7933600000000001</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="5">
         <v>0.71606000000000003</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="5">
         <v>-0.24948999999999999</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="5">
         <v>0.81501000000000001</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G44" s="5">
         <v>0.40762999999999999</v>
       </c>
-      <c r="H44" s="6">
+      <c r="H44" s="5">
         <v>-1.05721</v>
       </c>
-      <c r="I44" s="4">
+      <c r="I44" s="5">
         <v>-0.77649000000000001</v>
       </c>
-      <c r="J44" s="4">
+      <c r="J44" s="5">
         <v>0.26495000000000002</v>
       </c>
-      <c r="K44" s="4">
+      <c r="K44" s="5">
         <v>1.26172</v>
       </c>
-      <c r="L44" s="4">
+      <c r="L44" s="5">
         <v>-0.32966000000000001</v>
       </c>
-      <c r="M44" s="4">
+      <c r="M44" s="5">
         <v>4.6730000000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="5">
         <v>-1.31721</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="5">
         <v>-1.3907</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="5">
         <v>1.601E-2</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="5">
         <v>-0.86724000000000001</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="5">
         <v>-0.46872000000000003</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45" s="5">
         <v>-0.18113000000000001</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="5">
         <v>-0.46881</v>
       </c>
-      <c r="I45" s="4">
+      <c r="I45" s="5">
         <v>-0.38768999999999998</v>
       </c>
-      <c r="J45" s="4">
+      <c r="J45" s="5">
         <v>0.32468000000000002</v>
       </c>
-      <c r="K45" s="4">
+      <c r="K45" s="5">
         <v>1.92923</v>
       </c>
-      <c r="L45" s="4">
+      <c r="L45" s="5">
         <v>-0.11426</v>
       </c>
-      <c r="M45" s="4">
+      <c r="M45" s="5">
         <v>-1.1469999999999999E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="5">
         <v>-1.10883</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="5">
         <v>-1.67981</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="5">
         <v>0.20437</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="5">
         <v>-1.4977499999999999</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="5">
         <v>0.32743</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G46" s="5">
         <v>-0.20050999999999999</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="5">
         <v>-0.80669000000000002</v>
       </c>
-      <c r="I46" s="4">
+      <c r="I46" s="5">
         <v>-6.2549999999999994E-2</v>
       </c>
-      <c r="J46" s="4">
+      <c r="J46" s="5">
         <v>0.31208000000000002</v>
       </c>
-      <c r="K46" s="4">
+      <c r="K46" s="5">
         <v>2.38524</v>
       </c>
-      <c r="L46" s="4">
+      <c r="L46" s="5">
         <v>-0.18032999999999999</v>
       </c>
-      <c r="M46" s="4">
+      <c r="M46" s="5">
         <v>-1.1180000000000001E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="5">
         <v>-1.4170100000000001</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="5">
         <v>-1.4486399999999999</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="5">
         <v>-0.41195999999999999</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="5">
         <v>-0.96721999999999997</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="5">
         <v>-0.34702</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G47" s="5">
         <v>0.34373999999999999</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47" s="5">
         <v>-0.24193999999999999</v>
       </c>
-      <c r="I47" s="4">
+      <c r="I47" s="5">
         <v>-0.66361999999999999</v>
       </c>
-      <c r="J47" s="4">
+      <c r="J47" s="5">
         <v>0.20016</v>
       </c>
-      <c r="K47" s="4">
+      <c r="K47" s="5">
         <v>2.3376299999999999</v>
       </c>
-      <c r="L47" s="4">
+      <c r="L47" s="5">
         <v>8.6169999999999997E-2</v>
       </c>
-      <c r="M47" s="4">
+      <c r="M47" s="5">
         <v>-1.686E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="5">
         <v>-0.90422999999999998</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="5">
         <v>1.5898300000000001</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="5">
         <v>0.17777999999999999</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="5">
         <v>-1.17801</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="5">
         <v>0.50836000000000003</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G48" s="5">
         <v>0.66059000000000001</v>
       </c>
-      <c r="H48" s="6">
+      <c r="H48" s="5">
         <v>-0.99185000000000001</v>
       </c>
-      <c r="I48" s="4">
+      <c r="I48" s="5">
         <v>-1.9404699999999999</v>
       </c>
-      <c r="J48" s="4">
+      <c r="J48" s="5">
         <v>0.192</v>
       </c>
-      <c r="K48" s="4">
+      <c r="K48" s="5">
         <v>2.6263299999999998</v>
       </c>
-      <c r="L48" s="4">
+      <c r="L48" s="5">
         <v>-0.14108999999999999</v>
       </c>
-      <c r="M48" s="4">
+      <c r="M48" s="5">
         <v>-5.525E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="5">
         <v>-1.1034299999999999</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="5">
         <v>-1.3422099999999999</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="5">
         <v>-5.1399999999999996E-3</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="5">
         <v>-1.2795700000000001</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="5">
         <v>0.62111000000000005</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G49" s="5">
         <v>0.39621000000000001</v>
       </c>
-      <c r="H49" s="6">
+      <c r="H49" s="5">
         <v>-0.24557000000000001</v>
       </c>
-      <c r="I49" s="4">
+      <c r="I49" s="5">
         <v>-1.10954</v>
       </c>
-      <c r="J49" s="4">
+      <c r="J49" s="5">
         <v>0.33804000000000001</v>
       </c>
-      <c r="K49" s="4">
+      <c r="K49" s="5">
         <v>2.0803600000000002</v>
       </c>
-      <c r="L49" s="4">
+      <c r="L49" s="5">
         <v>-0.13044</v>
       </c>
-      <c r="M49" s="4">
+      <c r="M49" s="5">
         <v>-0.11656999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="5">
         <v>-1.2937399999999999</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="5">
         <v>-0.27978999999999998</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="5">
         <v>-0.24759</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="5">
         <v>-1.1312800000000001</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="5">
         <v>0.82257000000000002</v>
       </c>
-      <c r="G50" s="4">
+      <c r="G50" s="5">
         <v>0.27937000000000001</v>
       </c>
-      <c r="H50" s="6">
+      <c r="H50" s="5">
         <v>-0.56179000000000001</v>
       </c>
-      <c r="I50" s="4">
+      <c r="I50" s="5">
         <v>-2.2860299999999998</v>
       </c>
-      <c r="J50" s="4">
+      <c r="J50" s="5">
         <v>0.16855000000000001</v>
       </c>
-      <c r="K50" s="4">
+      <c r="K50" s="5">
         <v>2.3959100000000002</v>
       </c>
-      <c r="L50" s="4">
+      <c r="L50" s="5">
         <v>-6.6629999999999995E-2</v>
       </c>
-      <c r="M50" s="4">
+      <c r="M50" s="5">
         <v>-4.1700000000000001E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="5">
         <v>-0.66220000000000001</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="5">
         <v>1.6597900000000001</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="5">
         <v>0.31236999999999998</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="5">
         <v>-0.27152999999999999</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="5">
         <v>0.65561999999999998</v>
       </c>
-      <c r="G51" s="4">
+      <c r="G51" s="5">
         <v>0.78100999999999998</v>
       </c>
-      <c r="H51" s="6">
+      <c r="H51" s="5">
         <v>-1.0898399999999999</v>
       </c>
-      <c r="I51" s="4">
+      <c r="I51" s="5">
         <v>-1.3875299999999999</v>
       </c>
-      <c r="J51" s="4">
+      <c r="J51" s="5">
         <v>0.12245</v>
       </c>
-      <c r="K51" s="4">
+      <c r="K51" s="5">
         <v>0.99875000000000003</v>
       </c>
-      <c r="L51" s="4">
+      <c r="L51" s="5">
         <v>-0.15206</v>
       </c>
-      <c r="M51" s="4">
+      <c r="M51" s="5">
         <v>-0.13059999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="5">
         <v>-0.78098000000000001</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="5">
         <v>1.7802500000000001</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="5">
         <v>0.92503999999999997</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E52" s="5">
         <v>-0.17588999999999999</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="5">
         <v>0.85670000000000002</v>
       </c>
-      <c r="G52" s="4">
+      <c r="G52" s="5">
         <v>0.88829000000000002</v>
       </c>
-      <c r="H52" s="6">
+      <c r="H52" s="5">
         <v>-1.2143699999999999</v>
       </c>
-      <c r="I52" s="4">
+      <c r="I52" s="5">
         <v>-1.14514</v>
       </c>
-      <c r="J52" s="4">
+      <c r="J52" s="5">
         <v>0.24909000000000001</v>
       </c>
-      <c r="K52" s="4">
+      <c r="K52" s="5">
         <v>1.4329000000000001</v>
       </c>
-      <c r="L52" s="4">
+      <c r="L52" s="5">
         <v>-7.7280000000000001E-2</v>
       </c>
-      <c r="M52" s="4">
+      <c r="M52" s="5">
         <v>-5.1889999999999999E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="5">
         <v>-0.55376000000000003</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="5">
         <v>1.55755</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="5">
         <v>0.33178999999999997</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53" s="5">
         <v>-0.37086000000000002</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="5">
         <v>0.83738000000000001</v>
       </c>
-      <c r="G53" s="4">
+      <c r="G53" s="5">
         <v>0.80291000000000001</v>
       </c>
-      <c r="H53" s="6">
+      <c r="H53" s="5">
         <v>-1.0318099999999999</v>
       </c>
-      <c r="I53" s="4">
+      <c r="I53" s="5">
         <v>-1.06511</v>
       </c>
-      <c r="J53" s="4">
+      <c r="J53" s="5">
         <v>9.6269999999999994E-2</v>
       </c>
-      <c r="K53" s="4">
+      <c r="K53" s="5">
         <v>1.44051</v>
       </c>
-      <c r="L53" s="4">
+      <c r="L53" s="5">
         <v>-0.15844</v>
       </c>
-      <c r="M53" s="4">
+      <c r="M53" s="5">
         <v>-0.13119</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="5">
         <v>-0.75019999999999998</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="5">
         <v>2.6706599999999998</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="5">
         <v>0.11309</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="5">
         <v>-0.62075000000000002</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="5">
         <v>0.53081</v>
       </c>
-      <c r="G54" s="4">
+      <c r="G54" s="5">
         <v>0.85643000000000002</v>
       </c>
-      <c r="H54" s="6">
+      <c r="H54" s="5">
         <v>-1.1021399999999999</v>
       </c>
-      <c r="I54" s="4">
+      <c r="I54" s="5">
         <v>-0.70901000000000003</v>
       </c>
-      <c r="J54" s="4">
+      <c r="J54" s="5">
         <v>0.22422</v>
       </c>
-      <c r="K54" s="4">
+      <c r="K54" s="5">
         <v>1.9297200000000001</v>
       </c>
-      <c r="L54" s="4">
+      <c r="L54" s="5">
         <v>-2.681E-2</v>
       </c>
-      <c r="M54" s="4">
+      <c r="M54" s="5">
         <v>-6.4240000000000005E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="5">
         <v>-0.74238000000000004</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="5">
         <v>1.37747</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="5">
         <v>0.26805000000000001</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="5">
         <v>-0.41436000000000001</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55" s="5">
         <v>0.64176</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G55" s="5">
         <v>0.69242000000000004</v>
       </c>
-      <c r="H55" s="6">
+      <c r="H55" s="5">
         <v>-0.87670000000000003</v>
       </c>
-      <c r="I55" s="4">
+      <c r="I55" s="5">
         <v>-1.5371699999999999</v>
       </c>
-      <c r="J55" s="4">
+      <c r="J55" s="5">
         <v>0.32181999999999999</v>
       </c>
-      <c r="K55" s="4">
+      <c r="K55" s="5">
         <v>1.2567699999999999</v>
       </c>
-      <c r="L55" s="4">
+      <c r="L55" s="5">
         <v>-0.29636000000000001</v>
       </c>
-      <c r="M55" s="4">
+      <c r="M55" s="5">
         <v>-0.11879000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="5">
         <v>-1.41622</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="5">
         <v>-1.35989</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="5">
         <v>0.49380000000000002</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="5">
         <v>-1.5841099999999999</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="5">
         <v>0.49720999999999999</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G56" s="5">
         <v>0.57604</v>
       </c>
-      <c r="H56" s="6">
+      <c r="H56" s="5">
         <v>-0.40747</v>
       </c>
-      <c r="I56" s="4">
+      <c r="I56" s="5">
         <v>-1.2265900000000001</v>
       </c>
-      <c r="J56" s="4">
+      <c r="J56" s="5">
         <v>8.1449999999999995E-2</v>
       </c>
-      <c r="K56" s="4">
+      <c r="K56" s="5">
         <v>3.9453100000000001</v>
       </c>
-      <c r="L56" s="4">
+      <c r="L56" s="5">
         <v>-0.29224</v>
       </c>
-      <c r="M56" s="4">
+      <c r="M56" s="5">
         <v>-5.0499999999999998E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="5">
         <v>-1.45848</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="5">
         <v>-1.5768500000000001</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="5">
         <v>5.75579E-4</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="5">
         <v>-1.1490400000000001</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="5">
         <v>8.3790000000000003E-2</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G57" s="5">
         <v>0.19725000000000001</v>
       </c>
-      <c r="H57" s="6">
+      <c r="H57" s="5">
         <v>-0.19283</v>
       </c>
-      <c r="I57" s="4">
+      <c r="I57" s="5">
         <v>-0.66710999999999998</v>
       </c>
-      <c r="J57" s="4">
+      <c r="J57" s="5">
         <v>0.23422000000000001</v>
       </c>
-      <c r="K57" s="4">
+      <c r="K57" s="5">
         <v>2.0696400000000001</v>
       </c>
-      <c r="L57" s="4">
+      <c r="L57" s="5">
         <v>-5.7910000000000003E-2</v>
       </c>
-      <c r="M57" s="4">
+      <c r="M57" s="5">
         <v>-3.5430000000000003E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="5">
         <v>-1.3460300000000001</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="5">
         <v>-1.26146</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="5">
         <v>-1.7729999999999999E-2</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E58" s="5">
         <v>-0.87509999999999999</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="5">
         <v>0.31326999999999999</v>
       </c>
-      <c r="G58" s="4">
+      <c r="G58" s="5">
         <v>0.53371999999999997</v>
       </c>
-      <c r="H58" s="6">
+      <c r="H58" s="5">
         <v>-0.58050999999999997</v>
       </c>
-      <c r="I58" s="4">
+      <c r="I58" s="5">
         <v>-1.1214999999999999</v>
       </c>
-      <c r="J58" s="4">
+      <c r="J58" s="5">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="K58" s="4">
+      <c r="K58" s="5">
         <v>1.7685299999999999</v>
       </c>
-      <c r="L58" s="4">
+      <c r="L58" s="5">
         <v>-0.19905</v>
       </c>
-      <c r="M58" s="4">
+      <c r="M58" s="5">
         <v>-9.2189999999999994E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="5">
         <v>-1.2930600000000001</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="5">
         <v>-1.28186</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="5">
         <v>0.24475</v>
       </c>
-      <c r="E59" s="4">
+      <c r="E59" s="5">
         <v>-0.97460000000000002</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="5">
         <v>0.65149999999999997</v>
       </c>
-      <c r="G59" s="4">
+      <c r="G59" s="5">
         <v>0.37752000000000002</v>
       </c>
-      <c r="H59" s="6">
+      <c r="H59" s="5">
         <v>-0.50148000000000004</v>
       </c>
-      <c r="I59" s="4">
+      <c r="I59" s="5">
         <v>-0.91186999999999996</v>
       </c>
-      <c r="J59" s="4">
+      <c r="J59" s="5">
         <v>8.43E-3</v>
       </c>
-      <c r="K59" s="4">
+      <c r="K59" s="5">
         <v>1.39683</v>
       </c>
-      <c r="L59" s="4">
+      <c r="L59" s="5">
         <v>-0.19572000000000001</v>
       </c>
-      <c r="M59" s="4">
+      <c r="M59" s="5">
         <v>-8.6889999999999995E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="5">
         <v>-0.89495000000000002</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="5">
         <v>2.4396300000000002</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="5">
         <v>0.22559000000000001</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E60" s="5">
         <v>-4.1619999999999997E-2</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="5">
         <v>0.81391999999999998</v>
       </c>
-      <c r="G60" s="4">
+      <c r="G60" s="5">
         <v>0.90324000000000004</v>
       </c>
-      <c r="H60" s="6">
+      <c r="H60" s="5">
         <v>-1.0755600000000001</v>
       </c>
-      <c r="I60" s="4">
+      <c r="I60" s="5">
         <v>-1.0726</v>
       </c>
-      <c r="J60" s="4">
+      <c r="J60" s="5">
         <v>8.831E-2</v>
       </c>
-      <c r="K60" s="4">
+      <c r="K60" s="5">
         <v>1.30094</v>
       </c>
-      <c r="L60" s="4">
+      <c r="L60" s="5">
         <v>-0.24052000000000001</v>
       </c>
-      <c r="M60" s="4">
+      <c r="M60" s="5">
         <v>-0.17080999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="5">
         <v>-0.71077000000000001</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="5">
         <v>3.3084199999999999</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="5">
         <v>0.27801999999999999</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E61" s="5">
         <v>-0.13976</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="5">
         <v>0.79610999999999998</v>
       </c>
-      <c r="G61" s="4">
+      <c r="G61" s="5">
         <v>1.02826</v>
       </c>
-      <c r="H61" s="6">
+      <c r="H61" s="5">
         <v>-1.0949899999999999</v>
       </c>
-      <c r="I61" s="4">
+      <c r="I61" s="5">
         <v>-1.23969</v>
       </c>
-      <c r="J61" s="4">
+      <c r="J61" s="5">
         <v>0.21185999999999999</v>
       </c>
-      <c r="K61" s="4">
+      <c r="K61" s="5">
         <v>1.2914300000000001</v>
       </c>
-      <c r="L61" s="4">
+      <c r="L61" s="5">
         <v>-9.3840000000000007E-2</v>
       </c>
-      <c r="M61" s="4">
+      <c r="M61" s="5">
         <v>-0.11452</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="5">
         <v>-0.27816000000000002</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="5">
         <v>0.56037000000000003</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="5">
         <v>-0.93008000000000002</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E62" s="5">
         <v>-1.57605</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F62" s="5">
         <v>7.9390000000000002E-2</v>
       </c>
-      <c r="G62" s="4">
+      <c r="G62" s="5">
         <v>-3.81E-3</v>
       </c>
-      <c r="H62" s="6">
+      <c r="H62" s="5">
         <v>-1.78573</v>
       </c>
-      <c r="I62" s="4">
+      <c r="I62" s="5">
         <v>-1.1121300000000001</v>
       </c>
-      <c r="J62" s="4">
+      <c r="J62" s="5">
         <v>0.21929000000000001</v>
       </c>
-      <c r="K62" s="4">
+      <c r="K62" s="5">
         <v>1.18872</v>
       </c>
-      <c r="L62" s="4">
+      <c r="L62" s="5">
         <v>-2.845E-2</v>
       </c>
-      <c r="M62" s="4">
+      <c r="M62" s="5">
         <v>-0.10023</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="5">
         <v>0.54386999999999996</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="5">
         <v>0.57933000000000001</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="5">
         <v>0.87522999999999995</v>
       </c>
-      <c r="E63" s="4">
+      <c r="E63" s="5">
         <v>-1.8242400000000001</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="5">
         <v>0.26229999999999998</v>
       </c>
-      <c r="G63" s="4">
+      <c r="G63" s="5">
         <v>0.82126999999999994</v>
       </c>
-      <c r="H63" s="6">
+      <c r="H63" s="5">
         <v>-1.0785100000000001</v>
       </c>
-      <c r="I63" s="4">
+      <c r="I63" s="5">
         <v>0.20224</v>
       </c>
-      <c r="J63" s="4">
+      <c r="J63" s="5">
         <v>0.44395000000000001</v>
       </c>
-      <c r="K63" s="4">
+      <c r="K63" s="5">
         <v>2.2413400000000001</v>
       </c>
-      <c r="L63" s="4">
+      <c r="L63" s="5">
         <v>0.19478999999999999</v>
       </c>
-      <c r="M63" s="4">
+      <c r="M63" s="5">
         <v>0.24940999999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="5">
         <v>0.11405999999999999</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="5">
         <v>1.56586</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="5">
         <v>-3.177E-2</v>
       </c>
-      <c r="E64" s="4">
+      <c r="E64" s="5">
         <v>-0.96228000000000002</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="5">
         <v>0.26162000000000002</v>
       </c>
-      <c r="G64" s="4">
+      <c r="G64" s="5">
         <v>0.75914000000000004</v>
       </c>
-      <c r="H64" s="6">
+      <c r="H64" s="5">
         <v>-1.696</v>
       </c>
-      <c r="I64" s="4">
+      <c r="I64" s="5">
         <v>-0.98153000000000001</v>
       </c>
-      <c r="J64" s="4">
+      <c r="J64" s="5">
         <v>0.14904999999999999</v>
       </c>
-      <c r="K64" s="4">
+      <c r="K64" s="5">
         <v>0.68815999999999999</v>
       </c>
-      <c r="L64" s="4">
+      <c r="L64" s="5">
         <v>0.17324999999999999</v>
       </c>
-      <c r="M64" s="4">
+      <c r="M64" s="5">
         <v>8.4320000000000006E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="5">
         <v>1.1220600000000001</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="5">
         <v>1.2519</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="5">
         <v>1.0509200000000001</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E65" s="5">
         <v>-0.75631000000000004</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F65" s="5">
         <v>0.63704000000000005</v>
       </c>
-      <c r="G65" s="4">
+      <c r="G65" s="5">
         <v>1.39262</v>
       </c>
-      <c r="H65" s="6">
+      <c r="H65" s="5">
         <v>-1.42231</v>
       </c>
-      <c r="I65" s="4">
+      <c r="I65" s="5">
         <v>-0.33176</v>
       </c>
-      <c r="J65" s="4">
+      <c r="J65" s="5">
         <v>0.30714999999999998</v>
       </c>
-      <c r="K65" s="4">
+      <c r="K65" s="5">
         <v>1.29155</v>
       </c>
-      <c r="L65" s="4">
+      <c r="L65" s="5">
         <v>0.28465000000000001</v>
       </c>
-      <c r="M65" s="4">
+      <c r="M65" s="5">
         <v>0.26737</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="5">
         <v>-0.65698999999999996</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="5">
         <v>0.69506999999999997</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66" s="5">
         <v>-0.66613999999999995</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E66" s="5">
         <v>-1.55694</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="5">
         <v>4.4400000000000004E-3</v>
       </c>
-      <c r="G66" s="4">
+      <c r="G66" s="5">
         <v>6.8760000000000002E-2</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H66" s="5">
         <v>-2.0670500000000001</v>
       </c>
-      <c r="I66" s="4">
+      <c r="I66" s="5">
         <v>-0.79791999999999996</v>
       </c>
-      <c r="J66" s="4">
+      <c r="J66" s="5">
         <v>0.18592</v>
       </c>
-      <c r="K66" s="4">
+      <c r="K66" s="5">
         <v>2.05382</v>
       </c>
-      <c r="L66" s="4">
+      <c r="L66" s="5">
         <v>0.22878000000000001</v>
       </c>
-      <c r="M66" s="4">
+      <c r="M66" s="5">
         <v>-5.8819999999999997E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="5">
         <v>0.37058999999999997</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="5">
         <v>1.5069900000000001</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D67" s="5">
         <v>0.31368000000000001</v>
       </c>
-      <c r="E67" s="4">
+      <c r="E67" s="5">
         <v>-1.19221</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="5">
         <v>0.36325000000000002</v>
       </c>
-      <c r="G67" s="4">
+      <c r="G67" s="5">
         <v>0.56701000000000001</v>
       </c>
-      <c r="H67" s="6">
+      <c r="H67" s="5">
         <v>-1.45225</v>
       </c>
-      <c r="I67" s="4">
+      <c r="I67" s="5">
         <v>-1.1844699999999999</v>
       </c>
-      <c r="J67" s="4">
+      <c r="J67" s="5">
         <v>0.21093000000000001</v>
       </c>
-      <c r="K67" s="4">
+      <c r="K67" s="5">
         <v>1.79545</v>
       </c>
-      <c r="L67" s="4">
+      <c r="L67" s="5">
         <v>0.24453</v>
       </c>
-      <c r="M67" s="4">
+      <c r="M67" s="5">
         <v>6.5680000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="5">
         <v>-1.7290099999999999</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="5">
         <v>0.82165999999999995</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68" s="5">
         <v>-1.0515000000000001</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E68" s="5">
         <v>-1.0797000000000001</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F68" s="5">
         <v>0.24933</v>
       </c>
-      <c r="G68" s="4">
+      <c r="G68" s="5">
         <v>0.32305</v>
       </c>
-      <c r="H68" s="6">
+      <c r="H68" s="5">
         <v>-1.54887</v>
       </c>
-      <c r="I68" s="4">
+      <c r="I68" s="5">
         <v>-0.71545000000000003</v>
       </c>
-      <c r="J68" s="4">
+      <c r="J68" s="5">
         <v>0.57413000000000003</v>
       </c>
-      <c r="K68" s="4">
+      <c r="K68" s="5">
         <v>0.81949000000000005</v>
       </c>
-      <c r="L68" s="4">
+      <c r="L68" s="5">
         <v>8.8020000000000001E-2</v>
       </c>
-      <c r="M68" s="4">
+      <c r="M68" s="5">
         <v>-0.11607000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="5">
         <v>-1.6384799999999999</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="5">
         <v>1.72943</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="5">
         <v>-0.97526999999999997</v>
       </c>
-      <c r="E69" s="4">
+      <c r="E69" s="5">
         <v>-0.91715000000000002</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F69" s="5">
         <v>0.37785000000000002</v>
       </c>
-      <c r="G69" s="4">
+      <c r="G69" s="5">
         <v>0.72355000000000003</v>
       </c>
-      <c r="H69" s="6">
+      <c r="H69" s="5">
         <v>-1.50753</v>
       </c>
-      <c r="I69" s="4">
+      <c r="I69" s="5">
         <v>-0.69816</v>
       </c>
-      <c r="J69" s="4">
+      <c r="J69" s="5">
         <v>0.3695</v>
       </c>
-      <c r="K69" s="4">
+      <c r="K69" s="5">
         <v>1.3267</v>
       </c>
-      <c r="L69" s="4">
+      <c r="L69" s="5">
         <v>0.42874000000000001</v>
       </c>
-      <c r="M69" s="4">
+      <c r="M69" s="5">
         <v>-2.2630000000000001E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="5">
         <v>-1.62469</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="5">
         <v>1.6177699999999999</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70" s="5">
         <v>-1.09799</v>
       </c>
-      <c r="E70" s="4">
+      <c r="E70" s="5">
         <v>-1.12666</v>
       </c>
-      <c r="F70" s="4">
+      <c r="F70" s="5">
         <v>0.24118000000000001</v>
       </c>
-      <c r="G70" s="4">
+      <c r="G70" s="5">
         <v>0.76956999999999998</v>
       </c>
-      <c r="H70" s="6">
+      <c r="H70" s="5">
         <v>-2.07762</v>
       </c>
-      <c r="I70" s="4">
+      <c r="I70" s="5">
         <v>-1.01278</v>
       </c>
-      <c r="J70" s="4">
+      <c r="J70" s="5">
         <v>0.44689000000000001</v>
       </c>
-      <c r="K70" s="4">
+      <c r="K70" s="5">
         <v>1.0363599999999999</v>
       </c>
-      <c r="L70" s="4">
+      <c r="L70" s="5">
         <v>0.17735999999999999</v>
       </c>
-      <c r="M70" s="4">
+      <c r="M70" s="5">
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="5">
         <v>-0.94274999999999998</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="5">
         <v>1.4795499999999999</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71" s="5">
         <v>-0.69423999999999997</v>
       </c>
-      <c r="E71" s="4">
+      <c r="E71" s="5">
         <v>-1.16723</v>
       </c>
-      <c r="F71" s="4">
+      <c r="F71" s="5">
         <v>0.41271999999999998</v>
       </c>
-      <c r="G71" s="4">
+      <c r="G71" s="5">
         <v>0.50236999999999998</v>
       </c>
-      <c r="H71" s="6">
+      <c r="H71" s="5">
         <v>-1.0836699999999999</v>
       </c>
-      <c r="I71" s="4">
+      <c r="I71" s="5">
         <v>-0.51822999999999997</v>
       </c>
-      <c r="J71" s="4">
+      <c r="J71" s="5">
         <v>0.32956999999999997</v>
       </c>
-      <c r="K71" s="4">
+      <c r="K71" s="5">
         <v>1.2504900000000001</v>
       </c>
-      <c r="L71" s="4">
+      <c r="L71" s="5">
         <v>0.22645999999999999</v>
       </c>
-      <c r="M71" s="4">
+      <c r="M71" s="5">
         <v>5.3429999999999998E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="5">
         <v>-1.58091</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="5">
         <v>1.5886499999999999</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72" s="5">
         <v>-0.46922999999999998</v>
       </c>
-      <c r="E72" s="4">
+      <c r="E72" s="5">
         <v>-1.2214700000000001</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F72" s="5">
         <v>0.45358999999999999</v>
       </c>
-      <c r="G72" s="4">
+      <c r="G72" s="5">
         <v>0.90390000000000004</v>
       </c>
-      <c r="H72" s="6">
+      <c r="H72" s="5">
         <v>-1.4779</v>
       </c>
-      <c r="I72" s="4">
+      <c r="I72" s="5">
         <v>-0.40331</v>
       </c>
-      <c r="J72" s="4">
+      <c r="J72" s="5">
         <v>0.46933999999999998</v>
       </c>
-      <c r="K72" s="4">
+      <c r="K72" s="5">
         <v>1.7962199999999999</v>
       </c>
-      <c r="L72" s="4">
+      <c r="L72" s="5">
         <v>0.18468000000000001</v>
       </c>
-      <c r="M72" s="4">
+      <c r="M72" s="5">
         <v>0.14724000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="5">
         <v>-1.7436400000000001</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="5">
         <v>1.3662300000000001</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D73" s="5">
         <v>-1.0196499999999999</v>
       </c>
-      <c r="E73" s="4">
+      <c r="E73" s="5">
         <v>-0.93862999999999996</v>
       </c>
-      <c r="F73" s="4">
+      <c r="F73" s="5">
         <v>0.38118999999999997</v>
       </c>
-      <c r="G73" s="4">
+      <c r="G73" s="5">
         <v>0.65791999999999995</v>
       </c>
-      <c r="H73" s="6">
+      <c r="H73" s="5">
         <v>-1.78363</v>
       </c>
-      <c r="I73" s="4">
+      <c r="I73" s="5">
         <v>-0.87594000000000005</v>
       </c>
-      <c r="J73" s="4">
+      <c r="J73" s="5">
         <v>0.64049</v>
       </c>
-      <c r="K73" s="4">
+      <c r="K73" s="5">
         <v>0.94689999999999996</v>
       </c>
-      <c r="L73" s="4">
+      <c r="L73" s="5">
         <v>0.23064000000000001</v>
       </c>
-      <c r="M73" s="4">
+      <c r="M73" s="5">
         <v>-2.001E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="5">
         <v>0.30044999999999999</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="5">
         <v>1.7805500000000001</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74" s="5">
         <v>0.65408999999999995</v>
       </c>
-      <c r="E74" s="4">
+      <c r="E74" s="5">
         <v>-1.4532</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F74" s="5">
         <v>0.51732999999999996</v>
       </c>
-      <c r="G74" s="4">
+      <c r="G74" s="5">
         <v>0.91549000000000003</v>
       </c>
-      <c r="H74" s="6">
+      <c r="H74" s="5">
         <v>-1.4694</v>
       </c>
-      <c r="I74" s="4">
+      <c r="I74" s="5">
         <v>-0.77751999999999999</v>
       </c>
-      <c r="J74" s="4">
+      <c r="J74" s="5">
         <v>0.19339000000000001</v>
       </c>
-      <c r="K74" s="4">
+      <c r="K74" s="5">
         <v>2.21698</v>
       </c>
-      <c r="L74" s="4">
+      <c r="L74" s="5">
         <v>4.1980000000000003E-2</v>
       </c>
-      <c r="M74" s="4">
+      <c r="M74" s="5">
         <v>0.12911</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75" s="5">
         <v>-0.33622999999999997</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75" s="5">
         <v>0.94950000000000001</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75" s="5">
         <v>0.30614000000000002</v>
       </c>
-      <c r="E75" s="4">
+      <c r="E75" s="5">
         <v>-1.4003000000000001</v>
       </c>
-      <c r="F75" s="4">
+      <c r="F75" s="5">
         <v>0.28273999999999999</v>
       </c>
-      <c r="G75" s="4">
+      <c r="G75" s="5">
         <v>0.54825999999999997</v>
       </c>
-      <c r="H75" s="6">
+      <c r="H75" s="5">
         <v>-1.6550199999999999</v>
       </c>
-      <c r="I75" s="4">
+      <c r="I75" s="5">
         <v>-0.66008999999999995</v>
       </c>
-      <c r="J75" s="4">
+      <c r="J75" s="5">
         <v>0.22846</v>
       </c>
-      <c r="K75" s="4">
+      <c r="K75" s="5">
         <v>2.12697</v>
       </c>
-      <c r="L75" s="4">
+      <c r="L75" s="5">
         <v>4.3770000000000003E-2</v>
       </c>
-      <c r="M75" s="4">
+      <c r="M75" s="5">
         <v>0.18670999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="5">
         <v>0.87195</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="5">
         <v>1.7372399999999999</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D76" s="5">
         <v>0.62536000000000003</v>
       </c>
-      <c r="E76" s="4">
+      <c r="E76" s="5">
         <v>-1.6284700000000001</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F76" s="5">
         <v>0.33001999999999998</v>
       </c>
-      <c r="G76" s="4">
+      <c r="G76" s="5">
         <v>1.00159</v>
       </c>
-      <c r="H76" s="6">
+      <c r="H76" s="5">
         <v>-1.2565500000000001</v>
       </c>
-      <c r="I76" s="4">
+      <c r="I76" s="5">
         <v>-0.72762000000000004</v>
       </c>
-      <c r="J76" s="4">
+      <c r="J76" s="5">
         <v>0.33993000000000001</v>
       </c>
-      <c r="K76" s="4">
+      <c r="K76" s="5">
         <v>2.5489799999999998</v>
       </c>
-      <c r="L76" s="4">
+      <c r="L76" s="5">
         <v>0.16298000000000001</v>
       </c>
-      <c r="M76" s="4">
+      <c r="M76" s="5">
         <v>0.28004000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="5" t="s">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77" s="5">
         <v>6.4269999999999994E-2</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="5">
         <v>1.7006300000000001</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D77" s="5">
         <v>-5.6030000000000003E-2</v>
       </c>
-      <c r="E77" s="4">
+      <c r="E77" s="5">
         <v>-1.0752299999999999</v>
       </c>
-      <c r="F77" s="4">
+      <c r="F77" s="5">
         <v>0.50238000000000005</v>
       </c>
-      <c r="G77" s="4">
+      <c r="G77" s="5">
         <v>0.81172999999999995</v>
       </c>
-      <c r="H77" s="6">
+      <c r="H77" s="5">
         <v>-1.6113200000000001</v>
       </c>
-      <c r="I77" s="4">
+      <c r="I77" s="5">
         <v>-1.4603299999999999</v>
       </c>
-      <c r="J77" s="4">
+      <c r="J77" s="5">
         <v>0.14982999999999999</v>
       </c>
-      <c r="K77" s="4">
+      <c r="K77" s="5">
         <v>1.29216</v>
       </c>
-      <c r="L77" s="4">
+      <c r="L77" s="5">
         <v>0.37297000000000002</v>
       </c>
-      <c r="M77" s="4">
+      <c r="M77" s="5">
         <v>0.12698000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="5" t="s">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="5">
         <v>-0.10381</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="5">
         <v>1.0991200000000001</v>
       </c>
-      <c r="D78" s="4">
+      <c r="D78" s="5">
         <v>0.25996000000000002</v>
       </c>
-      <c r="E78" s="4">
+      <c r="E78" s="5">
         <v>-1.4366399999999999</v>
       </c>
-      <c r="F78" s="4">
+      <c r="F78" s="5">
         <v>0.26889000000000002</v>
       </c>
-      <c r="G78" s="4">
+      <c r="G78" s="5">
         <v>0.73860000000000003</v>
       </c>
-      <c r="H78" s="6">
+      <c r="H78" s="5">
         <v>-1.53294</v>
       </c>
-      <c r="I78" s="4">
+      <c r="I78" s="5">
         <v>-1.0687800000000001</v>
       </c>
-      <c r="J78" s="4">
+      <c r="J78" s="5">
         <v>0.20599999999999999</v>
       </c>
-      <c r="K78" s="4">
+      <c r="K78" s="5">
         <v>1.9022300000000001</v>
       </c>
-      <c r="L78" s="4">
+      <c r="L78" s="5">
         <v>3.2960000000000003E-2</v>
       </c>
-      <c r="M78" s="4">
+      <c r="M78" s="5">
         <v>0.12474</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79" s="5">
         <v>0.84330000000000005</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="5">
         <v>1.2326299999999999</v>
       </c>
-      <c r="D79" s="4">
+      <c r="D79" s="5">
         <v>0.82532000000000005</v>
       </c>
-      <c r="E79" s="4">
+      <c r="E79" s="5">
         <v>-1.5825800000000001</v>
       </c>
-      <c r="F79" s="4">
+      <c r="F79" s="5">
         <v>0.36374000000000001</v>
       </c>
-      <c r="G79" s="4">
+      <c r="G79" s="5">
         <v>1.01393</v>
       </c>
-      <c r="H79" s="6">
+      <c r="H79" s="5">
         <v>-1.3601700000000001</v>
       </c>
-      <c r="I79" s="4">
+      <c r="I79" s="5">
         <v>-0.85970000000000002</v>
       </c>
-      <c r="J79" s="4">
+      <c r="J79" s="5">
         <v>0.23035</v>
       </c>
-      <c r="K79" s="4">
+      <c r="K79" s="5">
         <v>2.4791699999999999</v>
       </c>
-      <c r="L79" s="4">
+      <c r="L79" s="5">
         <v>0.42114000000000001</v>
       </c>
-      <c r="M79" s="4">
+      <c r="M79" s="5">
         <v>0.20910999999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="5">
         <v>-0.42477999999999999</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80" s="5">
         <v>1.79938</v>
       </c>
-      <c r="D80" s="4">
+      <c r="D80" s="5">
         <v>-0.66252999999999995</v>
       </c>
-      <c r="E80" s="4">
+      <c r="E80" s="5">
         <v>-0.63529000000000002</v>
       </c>
-      <c r="F80" s="4">
+      <c r="F80" s="5">
         <v>0.46728999999999998</v>
       </c>
-      <c r="G80" s="4">
+      <c r="G80" s="5">
         <v>0.80961000000000005</v>
       </c>
-      <c r="H80" s="6">
+      <c r="H80" s="5">
         <v>-0.84992000000000001</v>
       </c>
-      <c r="I80" s="4">
+      <c r="I80" s="5">
         <v>-1.4176899999999999</v>
       </c>
-      <c r="J80" s="4">
+      <c r="J80" s="5">
         <v>0.57238</v>
       </c>
-      <c r="K80" s="4">
+      <c r="K80" s="5">
         <v>0.82118000000000002</v>
       </c>
-      <c r="L80" s="4">
+      <c r="L80" s="5">
         <v>0.35253000000000001</v>
       </c>
-      <c r="M80" s="4">
+      <c r="M80" s="5">
         <v>0.16627</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81" s="5">
         <v>-1.81494</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81" s="5">
         <v>1.4992099999999999</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D81" s="5">
         <v>-1.1259399999999999</v>
       </c>
-      <c r="E81" s="4">
+      <c r="E81" s="5">
         <v>-1.0402899999999999</v>
       </c>
-      <c r="F81" s="4">
+      <c r="F81" s="5">
         <v>0.39118000000000003</v>
       </c>
-      <c r="G81" s="4">
+      <c r="G81" s="5">
         <v>0.58652000000000004</v>
       </c>
-      <c r="H81" s="6">
+      <c r="H81" s="5">
         <v>-1.6991499999999999</v>
       </c>
-      <c r="I81" s="4">
+      <c r="I81" s="5">
         <v>-1.4641500000000001</v>
       </c>
-      <c r="J81" s="4">
+      <c r="J81" s="5">
         <v>0.54198999999999997</v>
       </c>
-      <c r="K81" s="4">
+      <c r="K81" s="5">
         <v>1.0265200000000001</v>
       </c>
-      <c r="L81" s="4">
+      <c r="L81" s="5">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="M81" s="4">
+      <c r="M81" s="5">
         <v>5.8090000000000003E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="5">
         <v>-2.0194000000000001</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82" s="5">
         <v>1.0533999999999999</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D82" s="5">
         <v>-1.3171200000000001</v>
       </c>
-      <c r="E82" s="4">
+      <c r="E82" s="5">
         <v>-1.3277000000000001</v>
       </c>
-      <c r="F82" s="4">
+      <c r="F82" s="5">
         <v>0.15129000000000001</v>
       </c>
-      <c r="G82" s="4">
+      <c r="G82" s="5">
         <v>0.25361</v>
       </c>
-      <c r="H82" s="6">
+      <c r="H82" s="5">
         <v>-1.8179700000000001</v>
       </c>
-      <c r="I82" s="4">
+      <c r="I82" s="5">
         <v>-0.63066999999999995</v>
       </c>
-      <c r="J82" s="4">
+      <c r="J82" s="5">
         <v>0.46848000000000001</v>
       </c>
-      <c r="K82" s="4">
+      <c r="K82" s="5">
         <v>1.49057</v>
       </c>
-      <c r="L82" s="4">
+      <c r="L82" s="5">
         <v>5.5070000000000001E-2</v>
       </c>
-      <c r="M82" s="4">
+      <c r="M82" s="5">
         <v>2.913E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="s">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83" s="5">
         <v>-1.6923299999999999</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83" s="5">
         <v>1.6949099999999999</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83" s="5">
         <v>-0.52973000000000003</v>
       </c>
-      <c r="E83" s="4">
+      <c r="E83" s="5">
         <v>-0.94506000000000001</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F83" s="5">
         <v>0.34649999999999997</v>
       </c>
-      <c r="G83" s="4">
+      <c r="G83" s="5">
         <v>0.88263000000000003</v>
       </c>
-      <c r="H83" s="6">
+      <c r="H83" s="5">
         <v>-1.5450999999999999</v>
       </c>
-      <c r="I83" s="4">
+      <c r="I83" s="5">
         <v>-0.64778999999999998</v>
       </c>
-      <c r="J83" s="4">
+      <c r="J83" s="5">
         <v>0.51185999999999998</v>
       </c>
-      <c r="K83" s="4">
+      <c r="K83" s="5">
         <v>1.25708</v>
       </c>
-      <c r="L83" s="4">
+      <c r="L83" s="5">
         <v>0.22914000000000001</v>
       </c>
-      <c r="M83" s="4">
+      <c r="M83" s="5">
         <v>0.14810000000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="5" t="s">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="5">
         <v>-1.43852</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84" s="5">
         <v>2.0183399999999998</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84" s="5">
         <v>-0.48720999999999998</v>
       </c>
-      <c r="E84" s="4">
+      <c r="E84" s="5">
         <v>-0.52761999999999998</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F84" s="5">
         <v>0.45629999999999998</v>
       </c>
-      <c r="G84" s="4">
+      <c r="G84" s="5">
         <v>0.80808999999999997</v>
       </c>
-      <c r="H84" s="6">
+      <c r="H84" s="5">
         <v>-1.4275800000000001</v>
       </c>
-      <c r="I84" s="4">
+      <c r="I84" s="5">
         <v>-1.7190700000000001</v>
       </c>
-      <c r="J84" s="4">
+      <c r="J84" s="5">
         <v>0.61511000000000005</v>
       </c>
-      <c r="K84" s="4">
+      <c r="K84" s="5">
         <v>1.01118</v>
       </c>
-      <c r="L84" s="4">
+      <c r="L84" s="5">
         <v>9.5100000000000004E-2</v>
       </c>
-      <c r="M84" s="4">
+      <c r="M84" s="5">
         <v>-6.9339999999999999E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85" s="5">
         <v>-1.87588</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85" s="5">
         <v>1.15892</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85" s="5">
         <v>-0.96457999999999999</v>
       </c>
-      <c r="E85" s="4">
+      <c r="E85" s="5">
         <v>-1.02505</v>
       </c>
-      <c r="F85" s="4">
+      <c r="F85" s="5">
         <v>0.18890000000000001</v>
       </c>
-      <c r="G85" s="4">
+      <c r="G85" s="5">
         <v>0.47039999999999998</v>
       </c>
-      <c r="H85" s="6">
+      <c r="H85" s="5">
         <v>-1.72149</v>
       </c>
-      <c r="I85" s="4">
+      <c r="I85" s="5">
         <v>-0.90486999999999995</v>
       </c>
-      <c r="J85" s="4">
+      <c r="J85" s="5">
         <v>0.43490000000000001</v>
       </c>
-      <c r="K85" s="4">
+      <c r="K85" s="5">
         <v>1.09406</v>
       </c>
-      <c r="L85" s="4">
+      <c r="L85" s="5">
         <v>0.24060000000000001</v>
       </c>
-      <c r="M85" s="4">
+      <c r="M85" s="5">
         <v>6.2239999999999997E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="5">
         <v>0.21068000000000001</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86" s="5">
         <v>1.22065</v>
       </c>
-      <c r="D86" s="4">
+      <c r="D86" s="5">
         <v>-0.76085999999999998</v>
       </c>
-      <c r="E86" s="4">
+      <c r="E86" s="5">
         <v>-1.5440799999999999</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="5">
         <v>0.48598999999999998</v>
       </c>
-      <c r="G86" s="4">
+      <c r="G86" s="5">
         <v>0.95132000000000005</v>
       </c>
-      <c r="H86" s="6">
+      <c r="H86" s="5">
         <v>-1.4000300000000001</v>
       </c>
-      <c r="I86" s="4">
+      <c r="I86" s="5">
         <v>-0.44993</v>
       </c>
-      <c r="J86" s="4">
+      <c r="J86" s="5">
         <v>0.54937000000000002</v>
       </c>
-      <c r="K86" s="4">
+      <c r="K86" s="5">
         <v>2.0052699999999999</v>
       </c>
-      <c r="L86" s="4">
+      <c r="L86" s="5">
         <v>0.16088</v>
       </c>
-      <c r="M86" s="4">
+      <c r="M86" s="5">
         <v>0.19067000000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="s">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87" s="5">
         <v>-0.27981</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87" s="5">
         <v>1.32484</v>
       </c>
-      <c r="D87" s="4">
+      <c r="D87" s="5">
         <v>-0.68442000000000003</v>
       </c>
-      <c r="E87" s="4">
+      <c r="E87" s="5">
         <v>-1.32481</v>
       </c>
-      <c r="F87" s="4">
+      <c r="F87" s="5">
         <v>0.46689999999999998</v>
       </c>
-      <c r="G87" s="4">
+      <c r="G87" s="5">
         <v>0.65693999999999997</v>
       </c>
-      <c r="H87" s="6">
+      <c r="H87" s="5">
         <v>-1.64134</v>
       </c>
-      <c r="I87" s="4">
+      <c r="I87" s="5">
         <v>-0.49326999999999999</v>
       </c>
-      <c r="J87" s="4">
+      <c r="J87" s="5">
         <v>0.43704999999999999</v>
       </c>
-      <c r="K87" s="4">
+      <c r="K87" s="5">
         <v>1.83575</v>
       </c>
-      <c r="L87" s="4">
+      <c r="L87" s="5">
         <v>0.16042000000000001</v>
       </c>
-      <c r="M87" s="4">
+      <c r="M87" s="5">
         <v>0.10945000000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="s">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="5">
         <v>0.11028</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C88" s="5">
         <v>1.3851100000000001</v>
       </c>
-      <c r="D88" s="4">
+      <c r="D88" s="5">
         <v>-0.45216000000000001</v>
       </c>
-      <c r="E88" s="4">
+      <c r="E88" s="5">
         <v>-1.5788</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F88" s="5">
         <v>0.44330000000000003</v>
       </c>
-      <c r="G88" s="4">
+      <c r="G88" s="5">
         <v>0.68435000000000001</v>
       </c>
-      <c r="H88" s="6">
+      <c r="H88" s="5">
         <v>-1.4453</v>
       </c>
-      <c r="I88" s="4">
+      <c r="I88" s="5">
         <v>-0.44671</v>
       </c>
-      <c r="J88" s="4">
+      <c r="J88" s="5">
         <v>0.47037000000000001</v>
       </c>
-      <c r="K88" s="4">
+      <c r="K88" s="5">
         <v>2.0960100000000002</v>
       </c>
-      <c r="L88" s="4">
+      <c r="L88" s="5">
         <v>0.14457</v>
       </c>
-      <c r="M88" s="4">
+      <c r="M88" s="5">
         <v>0.16669999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89" s="5">
         <v>0.11962</v>
       </c>
-      <c r="C89" s="4">
+      <c r="C89" s="5">
         <v>1.52101</v>
       </c>
-      <c r="D89" s="4">
+      <c r="D89" s="5">
         <v>-0.44753999999999999</v>
       </c>
-      <c r="E89" s="4">
+      <c r="E89" s="5">
         <v>-1.54895</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F89" s="5">
         <v>0.17035</v>
       </c>
-      <c r="G89" s="4">
+      <c r="G89" s="5">
         <v>0.83964000000000005</v>
       </c>
-      <c r="H89" s="6">
+      <c r="H89" s="5">
         <v>-1.4765600000000001</v>
       </c>
-      <c r="I89" s="4">
+      <c r="I89" s="5">
         <v>-0.64368000000000003</v>
       </c>
-      <c r="J89" s="4">
+      <c r="J89" s="5">
         <v>0.37175000000000002</v>
       </c>
-      <c r="K89" s="4">
+      <c r="K89" s="5">
         <v>2.2397399999999998</v>
       </c>
-      <c r="L89" s="4">
+      <c r="L89" s="5">
         <v>0.1595</v>
       </c>
-      <c r="M89" s="4">
+      <c r="M89" s="5">
         <v>0.16736999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="s">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="5">
         <v>0.46825</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90" s="5">
         <v>1.1039300000000001</v>
       </c>
-      <c r="D90" s="4">
+      <c r="D90" s="5">
         <v>-0.62492999999999999</v>
       </c>
-      <c r="E90" s="4">
+      <c r="E90" s="5">
         <v>-1.67757</v>
       </c>
-      <c r="F90" s="4">
+      <c r="F90" s="5">
         <v>0.43847999999999998</v>
       </c>
-      <c r="G90" s="4">
+      <c r="G90" s="5">
         <v>0.70969000000000004</v>
       </c>
-      <c r="H90" s="6">
+      <c r="H90" s="5">
         <v>-1.3175399999999999</v>
       </c>
-      <c r="I90" s="4">
+      <c r="I90" s="5">
         <v>-0.43284</v>
       </c>
-      <c r="J90" s="4">
+      <c r="J90" s="5">
         <v>0.52639000000000002</v>
       </c>
-      <c r="K90" s="4">
+      <c r="K90" s="5">
         <v>2.3564500000000002</v>
       </c>
-      <c r="L90" s="4">
+      <c r="L90" s="5">
         <v>9.9290000000000003E-2</v>
       </c>
-      <c r="M90" s="4">
+      <c r="M90" s="5">
         <v>0.1971</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="5" t="s">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91" s="5">
         <v>-1.93845</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C91" s="5">
         <v>0.88834000000000002</v>
       </c>
-      <c r="D91" s="4">
+      <c r="D91" s="5">
         <v>0.21374000000000001</v>
       </c>
-      <c r="E91" s="4">
+      <c r="E91" s="5">
         <v>-1.4277599999999999</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="5">
         <v>0.38030999999999998</v>
       </c>
-      <c r="G91" s="4">
+      <c r="G91" s="5">
         <v>0.28522999999999998</v>
       </c>
-      <c r="H91" s="6">
+      <c r="H91" s="5">
         <v>-1.4169700000000001</v>
       </c>
-      <c r="I91" s="4">
+      <c r="I91" s="5">
         <v>-0.28322000000000003</v>
       </c>
-      <c r="J91" s="4">
+      <c r="J91" s="5">
         <v>0.17648</v>
       </c>
-      <c r="K91" s="4">
+      <c r="K91" s="5">
         <v>1.41919</v>
       </c>
-      <c r="L91" s="4">
+      <c r="L91" s="5">
         <v>0.10363</v>
       </c>
-      <c r="M91" s="4">
+      <c r="M91" s="5">
         <v>5.5469999999999998E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="5" t="s">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="5">
         <v>-1.6867099999999999</v>
       </c>
-      <c r="C92" s="4">
+      <c r="C92" s="5">
         <v>1.7502500000000001</v>
       </c>
-      <c r="D92" s="4">
+      <c r="D92" s="5">
         <v>0.17985999999999999</v>
       </c>
-      <c r="E92" s="4">
+      <c r="E92" s="5">
         <v>-0.82594000000000001</v>
       </c>
-      <c r="F92" s="4">
+      <c r="F92" s="5">
         <v>0.36503999999999998</v>
       </c>
-      <c r="G92" s="4">
+      <c r="G92" s="5">
         <v>0.76897000000000004</v>
       </c>
-      <c r="H92" s="6">
+      <c r="H92" s="5">
         <v>-1.5041599999999999</v>
       </c>
-      <c r="I92" s="4">
+      <c r="I92" s="5">
         <v>-0.58220000000000005</v>
       </c>
-      <c r="J92" s="4">
+      <c r="J92" s="5">
         <v>0.18739</v>
       </c>
-      <c r="K92" s="4">
+      <c r="K92" s="5">
         <v>1.03942</v>
       </c>
-      <c r="L92" s="4">
+      <c r="L92" s="5">
         <v>0.18517</v>
       </c>
-      <c r="M92" s="4">
+      <c r="M92" s="5">
         <v>0.16606000000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" s="5" t="s">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B93" s="4">
+      <c r="B93" s="5">
         <v>-1.8238000000000001</v>
       </c>
-      <c r="C93" s="4">
+      <c r="C93" s="5">
         <v>1.0307299999999999</v>
       </c>
-      <c r="D93" s="4">
+      <c r="D93" s="5">
         <v>-0.19946</v>
       </c>
-      <c r="E93" s="4">
+      <c r="E93" s="5">
         <v>-1.1129500000000001</v>
       </c>
-      <c r="F93" s="4">
+      <c r="F93" s="5">
         <v>0.21833</v>
       </c>
-      <c r="G93" s="4">
+      <c r="G93" s="5">
         <v>0.29285</v>
       </c>
-      <c r="H93" s="6">
+      <c r="H93" s="5">
         <v>-1.5397400000000001</v>
       </c>
-      <c r="I93" s="4">
+      <c r="I93" s="5">
         <v>-0.50278999999999996</v>
       </c>
-      <c r="J93" s="4">
+      <c r="J93" s="5">
         <v>0.24853</v>
       </c>
-      <c r="K93" s="4">
+      <c r="K93" s="5">
         <v>1.1401699999999999</v>
       </c>
-      <c r="L93" s="4">
+      <c r="L93" s="5">
         <v>0.12296</v>
       </c>
-      <c r="M93" s="4">
+      <c r="M93" s="5">
         <v>-0.14446000000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A94" s="5" t="s">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="5">
         <v>-1.8168500000000001</v>
       </c>
-      <c r="C94" s="4">
+      <c r="C94" s="5">
         <v>1.31311</v>
       </c>
-      <c r="D94" s="4">
+      <c r="D94" s="5">
         <v>-0.23091</v>
       </c>
-      <c r="E94" s="4">
+      <c r="E94" s="5">
         <v>-1.15682</v>
       </c>
-      <c r="F94" s="4">
+      <c r="F94" s="5">
         <v>0.49303999999999998</v>
       </c>
-      <c r="G94" s="4">
+      <c r="G94" s="5">
         <v>0.52754000000000001</v>
       </c>
-      <c r="H94" s="6">
+      <c r="H94" s="5">
         <v>-1.5717300000000001</v>
       </c>
-      <c r="I94" s="4">
+      <c r="I94" s="5">
         <v>-0.56269999999999998</v>
       </c>
-      <c r="J94" s="4">
+      <c r="J94" s="5">
         <v>0.18334</v>
       </c>
-      <c r="K94" s="4">
+      <c r="K94" s="5">
         <v>1.34449</v>
       </c>
-      <c r="L94" s="4">
+      <c r="L94" s="5">
         <v>5.6439999999999997E-2</v>
       </c>
-      <c r="M94" s="4">
+      <c r="M94" s="5">
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B95" s="4">
+      <c r="B95" s="5">
         <v>-1.9618800000000001</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95" s="5">
         <v>1.0982499999999999</v>
       </c>
-      <c r="D95" s="4">
+      <c r="D95" s="5">
         <v>0.14338000000000001</v>
       </c>
-      <c r="E95" s="4">
+      <c r="E95" s="5">
         <v>-1.1783600000000001</v>
       </c>
-      <c r="F95" s="4">
+      <c r="F95" s="5">
         <v>0.41863</v>
       </c>
-      <c r="G95" s="4">
+      <c r="G95" s="5">
         <v>0.45017000000000001</v>
       </c>
-      <c r="H95" s="6">
+      <c r="H95" s="5">
         <v>-1.4464999999999999</v>
       </c>
-      <c r="I95" s="4">
+      <c r="I95" s="5">
         <v>-0.37724000000000002</v>
       </c>
-      <c r="J95" s="4">
+      <c r="J95" s="5">
         <v>0.22825000000000001</v>
       </c>
-      <c r="K95" s="4">
+      <c r="K95" s="5">
         <v>1.34551</v>
       </c>
-      <c r="L95" s="4">
+      <c r="L95" s="5">
         <v>0.11409999999999999</v>
       </c>
-      <c r="M95" s="4">
+      <c r="M95" s="5">
         <v>-0.11715</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="5" t="s">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="5">
         <v>-1.7638199999999999</v>
       </c>
-      <c r="C96" s="4">
+      <c r="C96" s="5">
         <v>1.0918699999999999</v>
       </c>
-      <c r="D96" s="4">
+      <c r="D96" s="5">
         <v>0.77897000000000005</v>
       </c>
-      <c r="E96" s="4">
+      <c r="E96" s="5">
         <v>-1.08873</v>
       </c>
-      <c r="F96" s="4">
+      <c r="F96" s="5">
         <v>0.44936999999999999</v>
       </c>
-      <c r="G96" s="4">
+      <c r="G96" s="5">
         <v>0.65761999999999998</v>
       </c>
-      <c r="H96" s="6">
+      <c r="H96" s="5">
         <v>-1.62252</v>
       </c>
-      <c r="I96" s="4">
+      <c r="I96" s="5">
         <v>-0.54230999999999996</v>
       </c>
-      <c r="J96" s="4">
+      <c r="J96" s="5">
         <v>0.28349000000000002</v>
       </c>
-      <c r="K96" s="4">
+      <c r="K96" s="5">
         <v>1.6151800000000001</v>
       </c>
-      <c r="L96" s="4">
+      <c r="L96" s="5">
         <v>3.9849999999999997E-2</v>
       </c>
-      <c r="M96" s="4">
+      <c r="M96" s="5">
         <v>0.12573999999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A97" s="5" t="s">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B97" s="4">
+      <c r="B97" s="5">
         <v>-0.31590000000000001</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97" s="5">
         <v>0.95969000000000004</v>
       </c>
-      <c r="D97" s="4">
+      <c r="D97" s="5">
         <v>0.86133000000000004</v>
       </c>
-      <c r="E97" s="4">
+      <c r="E97" s="5">
         <v>-1.51589</v>
       </c>
-      <c r="F97" s="4">
+      <c r="F97" s="5">
         <v>0.22073000000000001</v>
       </c>
-      <c r="G97" s="4">
+      <c r="G97" s="5">
         <v>0.49919000000000002</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H97" s="5">
         <v>-1.4916799999999999</v>
       </c>
-      <c r="I97" s="4">
+      <c r="I97" s="5">
         <v>-0.48025000000000001</v>
       </c>
-      <c r="J97" s="4">
+      <c r="J97" s="5">
         <v>0.33654000000000001</v>
       </c>
-      <c r="K97" s="4">
+      <c r="K97" s="5">
         <v>1.85178</v>
       </c>
-      <c r="L97" s="4">
+      <c r="L97" s="5">
         <v>0.24481</v>
       </c>
-      <c r="M97" s="4">
+      <c r="M97" s="5">
         <v>0.23538999999999999</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="5">
         <v>-0.33001000000000003</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98" s="5">
         <v>0.91113999999999995</v>
       </c>
-      <c r="D98" s="4">
+      <c r="D98" s="5">
         <v>0.14563000000000001</v>
       </c>
-      <c r="E98" s="4">
+      <c r="E98" s="5">
         <v>-1.7048700000000001</v>
       </c>
-      <c r="F98" s="4">
+      <c r="F98" s="5">
         <v>9.7259999999999999E-2</v>
       </c>
-      <c r="G98" s="4">
+      <c r="G98" s="5">
         <v>0.52871999999999997</v>
       </c>
-      <c r="H98" s="6">
+      <c r="H98" s="5">
         <v>-1.4953700000000001</v>
       </c>
-      <c r="I98" s="4">
+      <c r="I98" s="5">
         <v>-0.77602000000000004</v>
       </c>
-      <c r="J98" s="4">
+      <c r="J98" s="5">
         <v>0.32196999999999998</v>
       </c>
-      <c r="K98" s="4">
+      <c r="K98" s="5">
         <v>1.90252</v>
       </c>
-      <c r="L98" s="4">
+      <c r="L98" s="5">
         <v>2.1099999999999999E-3</v>
       </c>
-      <c r="M98" s="4">
+      <c r="M98" s="5">
         <v>0.11815000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B99" s="4">
+      <c r="B99" s="5">
         <v>-6.2469999999999998E-2</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99" s="5">
         <v>0.94094</v>
       </c>
-      <c r="D99" s="4">
+      <c r="D99" s="5">
         <v>0.68030000000000002</v>
       </c>
-      <c r="E99" s="4">
+      <c r="E99" s="5">
         <v>-1.53887</v>
       </c>
-      <c r="F99" s="4">
+      <c r="F99" s="5">
         <v>3.0190000000000002E-2</v>
       </c>
-      <c r="G99" s="4">
+      <c r="G99" s="5">
         <v>0.26845999999999998</v>
       </c>
-      <c r="H99" s="6">
+      <c r="H99" s="5">
         <v>-1.23054</v>
       </c>
-      <c r="I99" s="4">
+      <c r="I99" s="5">
         <v>-1.1597</v>
       </c>
-      <c r="J99" s="4">
+      <c r="J99" s="5">
         <v>0.46888000000000002</v>
       </c>
-      <c r="K99" s="4">
+      <c r="K99" s="5">
         <v>1.6683699999999999</v>
       </c>
-      <c r="L99" s="4">
+      <c r="L99" s="5">
         <v>-7.6780000000000001E-2</v>
       </c>
-      <c r="M99" s="4">
+      <c r="M99" s="5">
         <v>0.16491</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="5" t="s">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="5">
         <v>-0.13936000000000001</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100" s="5">
         <v>1.1475599999999999</v>
       </c>
-      <c r="D100" s="4">
+      <c r="D100" s="5">
         <v>0.16272</v>
       </c>
-      <c r="E100" s="4">
+      <c r="E100" s="5">
         <v>-1.51911</v>
       </c>
-      <c r="F100" s="4">
+      <c r="F100" s="5">
         <v>0.24462999999999999</v>
       </c>
-      <c r="G100" s="4">
+      <c r="G100" s="5">
         <v>0.84353999999999996</v>
       </c>
-      <c r="H100" s="6">
+      <c r="H100" s="5">
         <v>-1.57829</v>
       </c>
-      <c r="I100" s="4">
+      <c r="I100" s="5">
         <v>-1.0550299999999999</v>
       </c>
-      <c r="J100" s="4">
+      <c r="J100" s="5">
         <v>0.15872</v>
       </c>
-      <c r="K100" s="4">
+      <c r="K100" s="5">
         <v>2.2584</v>
       </c>
-      <c r="L100" s="4">
+      <c r="L100" s="5">
         <v>0.11078</v>
       </c>
-      <c r="M100" s="4">
+      <c r="M100" s="5">
         <v>0.11486</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B101" s="4">
+      <c r="B101" s="5">
         <v>-0.18376000000000001</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101" s="5">
         <v>0.87795999999999996</v>
       </c>
-      <c r="D101" s="4">
+      <c r="D101" s="5">
         <v>0.87234999999999996</v>
       </c>
-      <c r="E101" s="4">
+      <c r="E101" s="5">
         <v>-1.8783300000000001</v>
       </c>
-      <c r="F101" s="4">
+      <c r="F101" s="5">
         <v>0.10345</v>
       </c>
-      <c r="G101" s="4">
+      <c r="G101" s="5">
         <v>0.41377999999999998</v>
       </c>
-      <c r="H101" s="6">
+      <c r="H101" s="5">
         <v>-1.2139599999999999</v>
       </c>
-      <c r="I101" s="4">
+      <c r="I101" s="5">
         <v>-0.38951000000000002</v>
       </c>
-      <c r="J101" s="4">
+      <c r="J101" s="5">
         <v>0.40467999999999998</v>
       </c>
-      <c r="K101" s="4">
+      <c r="K101" s="5">
         <v>1.96167</v>
       </c>
-      <c r="L101" s="4">
+      <c r="L101" s="5">
         <v>0.17971999999999999</v>
       </c>
-      <c r="M101" s="4">
+      <c r="M101" s="5">
         <v>0.29263</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="5" t="s">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="5">
         <v>-1.7727200000000001</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102" s="5">
         <v>1.06531</v>
       </c>
-      <c r="D102" s="4">
+      <c r="D102" s="5">
         <v>-0.65125</v>
       </c>
-      <c r="E102" s="4">
+      <c r="E102" s="5">
         <v>-1.47048</v>
       </c>
-      <c r="F102" s="4">
+      <c r="F102" s="5">
         <v>0.19416</v>
       </c>
-      <c r="G102" s="4">
+      <c r="G102" s="5">
         <v>0.33241999999999999</v>
       </c>
-      <c r="H102" s="6">
+      <c r="H102" s="5">
         <v>-1.56779</v>
       </c>
-      <c r="I102" s="4">
+      <c r="I102" s="5">
         <v>-0.52480000000000004</v>
       </c>
-      <c r="J102" s="4">
+      <c r="J102" s="5">
         <v>0.44696999999999998</v>
       </c>
-      <c r="K102" s="4">
+      <c r="K102" s="5">
         <v>1.85039</v>
       </c>
-      <c r="L102" s="4">
+      <c r="L102" s="5">
         <v>0.13755000000000001</v>
       </c>
-      <c r="M102" s="4">
+      <c r="M102" s="5">
         <v>0.18248</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A103" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103" s="5">
         <v>-0.47560999999999998</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103" s="5">
         <v>1.9565300000000001</v>
       </c>
-      <c r="D103" s="4">
+      <c r="D103" s="5">
         <v>-0.62568999999999997</v>
       </c>
-      <c r="E103" s="4">
+      <c r="E103" s="5">
         <v>-0.90791999999999995</v>
       </c>
-      <c r="F103" s="4">
+      <c r="F103" s="5">
         <v>0.17455000000000001</v>
       </c>
-      <c r="G103" s="4">
+      <c r="G103" s="5">
         <v>0.40203</v>
       </c>
-      <c r="H103" s="6">
+      <c r="H103" s="5">
         <v>-0.8034</v>
       </c>
-      <c r="I103" s="4">
+      <c r="I103" s="5">
         <v>-1.3401700000000001</v>
       </c>
-      <c r="J103" s="4">
+      <c r="J103" s="5">
         <v>0.44291999999999998</v>
       </c>
-      <c r="K103" s="4">
+      <c r="K103" s="5">
         <v>1.1145799999999999</v>
       </c>
-      <c r="L103" s="4">
+      <c r="L103" s="5">
         <v>-0.13242999999999999</v>
       </c>
-      <c r="M103" s="4">
+      <c r="M103" s="5">
         <v>0.15412999999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A104" s="5" t="s">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="5">
         <v>-2.0097399999999999</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104" s="5">
         <v>0.68798999999999999</v>
       </c>
-      <c r="D104" s="4">
+      <c r="D104" s="5">
         <v>-0.53310999999999997</v>
       </c>
-      <c r="E104" s="4">
+      <c r="E104" s="5">
         <v>-1.4775700000000001</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="5">
         <v>0.34595999999999999</v>
       </c>
-      <c r="G104" s="4">
+      <c r="G104" s="5">
         <v>0.18651000000000001</v>
       </c>
-      <c r="H104" s="6">
+      <c r="H104" s="5">
         <v>-1.4373199999999999</v>
       </c>
-      <c r="I104" s="4">
+      <c r="I104" s="5">
         <v>-0.59082000000000001</v>
       </c>
-      <c r="J104" s="4">
+      <c r="J104" s="5">
         <v>0.42604999999999998</v>
       </c>
-      <c r="K104" s="4">
+      <c r="K104" s="5">
         <v>1.97231</v>
       </c>
-      <c r="L104" s="4">
+      <c r="L104" s="5">
         <v>-0.11373999999999999</v>
       </c>
-      <c r="M104" s="4">
+      <c r="M104" s="5">
         <v>0.13389000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A105" s="5" t="s">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105" s="5">
         <v>-1.6427700000000001</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105" s="5">
         <v>1.1645799999999999</v>
       </c>
-      <c r="D105" s="4">
+      <c r="D105" s="5">
         <v>-9.7769999999999996E-2</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E105" s="5">
         <v>-1.2373799999999999</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="5">
         <v>0.24956999999999999</v>
       </c>
-      <c r="G105" s="4">
+      <c r="G105" s="5">
         <v>0.32388</v>
       </c>
-      <c r="H105" s="6">
+      <c r="H105" s="5">
         <v>-1.23627</v>
       </c>
-      <c r="I105" s="4">
+      <c r="I105" s="5">
         <v>-0.60024999999999995</v>
       </c>
-      <c r="J105" s="4">
+      <c r="J105" s="5">
         <v>0.49704999999999999</v>
       </c>
-      <c r="K105" s="4">
+      <c r="K105" s="5">
         <v>1.6039300000000001</v>
       </c>
-      <c r="L105" s="4">
+      <c r="L105" s="5">
         <v>0.10777</v>
       </c>
-      <c r="M105" s="4">
+      <c r="M105" s="5">
         <v>0.12216</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A106" s="5" t="s">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A106" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="5">
         <v>-0.39573000000000003</v>
       </c>
-      <c r="C106" s="4">
+      <c r="C106" s="5">
         <v>1.62191</v>
       </c>
-      <c r="D106" s="4">
+      <c r="D106" s="5">
         <v>8.4700000000000001E-3</v>
       </c>
-      <c r="E106" s="4">
+      <c r="E106" s="5">
         <v>-1.20862</v>
       </c>
-      <c r="F106" s="4">
+      <c r="F106" s="5">
         <v>0.11547</v>
       </c>
-      <c r="G106" s="4">
+      <c r="G106" s="5">
         <v>0.51712999999999998</v>
       </c>
-      <c r="H106" s="6">
+      <c r="H106" s="5">
         <v>-0.81430000000000002</v>
       </c>
-      <c r="I106" s="4">
+      <c r="I106" s="5">
         <v>-0.84814000000000001</v>
       </c>
-      <c r="J106" s="4">
+      <c r="J106" s="5">
         <v>0.52141999999999999</v>
       </c>
-      <c r="K106" s="4">
+      <c r="K106" s="5">
         <v>2.0215700000000001</v>
       </c>
-      <c r="L106" s="4">
+      <c r="L106" s="5">
         <v>6.8430000000000005E-2</v>
       </c>
-      <c r="M106" s="4">
+      <c r="M106" s="5">
         <v>0.23665</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="5" t="s">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A107" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B107" s="4">
+      <c r="B107" s="5">
         <v>-1.36107</v>
       </c>
-      <c r="C107" s="4">
+      <c r="C107" s="5">
         <v>1.54121</v>
       </c>
-      <c r="D107" s="4">
+      <c r="D107" s="5">
         <v>-0.67967999999999995</v>
       </c>
-      <c r="E107" s="4">
+      <c r="E107" s="5">
         <v>-1.1094900000000001</v>
       </c>
-      <c r="F107" s="4">
+      <c r="F107" s="5">
         <v>0.43713000000000002</v>
       </c>
-      <c r="G107" s="4">
+      <c r="G107" s="5">
         <v>0.28710000000000002</v>
       </c>
-      <c r="H107" s="6">
+      <c r="H107" s="5">
         <v>-1.16154</v>
       </c>
-      <c r="I107" s="4">
+      <c r="I107" s="5">
         <v>-0.46523999999999999</v>
       </c>
-      <c r="J107" s="4">
+      <c r="J107" s="5">
         <v>8.2460000000000006E-2</v>
       </c>
-      <c r="K107" s="4">
+      <c r="K107" s="5">
         <v>2.1152199999999999</v>
       </c>
-      <c r="L107" s="4">
+      <c r="L107" s="5">
         <v>1.031E-2</v>
       </c>
-      <c r="M107" s="4">
+      <c r="M107" s="5">
         <v>1.034E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="5" t="s">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A108" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="5">
         <v>-1.0853600000000001</v>
       </c>
-      <c r="C108" s="4">
+      <c r="C108" s="5">
         <v>2.1091799999999998</v>
       </c>
-      <c r="D108" s="4">
+      <c r="D108" s="5">
         <v>-0.48258000000000001</v>
       </c>
-      <c r="E108" s="4">
+      <c r="E108" s="5">
         <v>-0.97108000000000005</v>
       </c>
-      <c r="F108" s="4">
+      <c r="F108" s="5">
         <v>0.54405999999999999</v>
       </c>
-      <c r="G108" s="4">
+      <c r="G108" s="5">
         <v>0.45623000000000002</v>
       </c>
-      <c r="H108" s="6">
+      <c r="H108" s="5">
         <v>-1.0600400000000001</v>
       </c>
-      <c r="I108" s="4">
+      <c r="I108" s="5">
         <v>-0.84667000000000003</v>
       </c>
-      <c r="J108" s="4">
+      <c r="J108" s="5">
         <v>0.26101999999999997</v>
       </c>
-      <c r="K108" s="4">
+      <c r="K108" s="5">
         <v>2.4913099999999999</v>
       </c>
-      <c r="L108" s="4">
+      <c r="L108" s="5">
         <v>5.577E-2</v>
       </c>
-      <c r="M108" s="4">
+      <c r="M108" s="5">
         <v>0.11840000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A109" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B109" s="4">
+      <c r="B109" s="5">
         <v>-1.2399100000000001</v>
       </c>
-      <c r="C109" s="4">
+      <c r="C109" s="5">
         <v>1.51715</v>
       </c>
-      <c r="D109" s="4">
+      <c r="D109" s="5">
         <v>-0.76454</v>
       </c>
-      <c r="E109" s="4">
+      <c r="E109" s="5">
         <v>-0.98143999999999998</v>
       </c>
-      <c r="F109" s="4">
+      <c r="F109" s="5">
         <v>0.44178000000000001</v>
       </c>
-      <c r="G109" s="4">
+      <c r="G109" s="5">
         <v>0.31592999999999999</v>
       </c>
-      <c r="H109" s="6">
+      <c r="H109" s="5">
         <v>-1.37839</v>
       </c>
-      <c r="I109" s="4">
+      <c r="I109" s="5">
         <v>-0.23401</v>
       </c>
-      <c r="J109" s="4">
+      <c r="J109" s="5">
         <v>0.24246999999999999</v>
       </c>
-      <c r="K109" s="4">
+      <c r="K109" s="5">
         <v>2.00861</v>
       </c>
-      <c r="L109" s="4">
+      <c r="L109" s="5">
         <v>-2.9739999999999999E-2</v>
       </c>
-      <c r="M109" s="4">
+      <c r="M109" s="5">
         <v>5.9300000000000004E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A110" s="5" t="s">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A110" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="5">
         <v>-1.13208</v>
       </c>
-      <c r="C110" s="4">
+      <c r="C110" s="5">
         <v>1.50719</v>
       </c>
-      <c r="D110" s="4">
+      <c r="D110" s="5">
         <v>-0.74345000000000006</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E110" s="5">
         <v>-0.96669000000000005</v>
       </c>
-      <c r="F110" s="4">
+      <c r="F110" s="5">
         <v>0.42164000000000001</v>
       </c>
-      <c r="G110" s="4">
+      <c r="G110" s="5">
         <v>0.51824000000000003</v>
       </c>
-      <c r="H110" s="6">
+      <c r="H110" s="5">
         <v>-1.2383999999999999</v>
       </c>
-      <c r="I110" s="4">
+      <c r="I110" s="5">
         <v>-1.1852499999999999</v>
       </c>
-      <c r="J110" s="4">
+      <c r="J110" s="5">
         <v>0.28205000000000002</v>
       </c>
-      <c r="K110" s="4">
+      <c r="K110" s="5">
         <v>2.1912199999999999</v>
       </c>
-      <c r="L110" s="4">
+      <c r="L110" s="5">
         <v>7.2840000000000002E-2</v>
       </c>
-      <c r="M110" s="4">
+      <c r="M110" s="5">
         <v>8.9770000000000003E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A111" s="5" t="s">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A111" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111" s="5">
         <v>-1.08108</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111" s="5">
         <v>1.8310900000000001</v>
       </c>
-      <c r="D111" s="4">
+      <c r="D111" s="5">
         <v>-0.82142999999999999</v>
       </c>
-      <c r="E111" s="4">
+      <c r="E111" s="5">
         <v>-0.87909999999999999</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="5">
         <v>0.49364999999999998</v>
       </c>
-      <c r="G111" s="4">
+      <c r="G111" s="5">
         <v>0.54037999999999997</v>
       </c>
-      <c r="H111" s="6">
+      <c r="H111" s="5">
         <v>-1.36036</v>
       </c>
-      <c r="I111" s="4">
+      <c r="I111" s="5">
         <v>-0.91590000000000005</v>
       </c>
-      <c r="J111" s="4">
+      <c r="J111" s="5">
         <v>0.16828000000000001</v>
       </c>
-      <c r="K111" s="4">
+      <c r="K111" s="5">
         <v>1.7992699999999999</v>
       </c>
-      <c r="L111" s="4">
+      <c r="L111" s="5">
         <v>0.10632</v>
       </c>
-      <c r="M111" s="4">
+      <c r="M111" s="5">
         <v>4.5569999999999999E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A112" s="5" t="s">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A112" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="5">
         <v>-0.94615000000000005</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C112" s="5">
         <v>2.2292299999999998</v>
       </c>
-      <c r="D112" s="4">
+      <c r="D112" s="5">
         <v>-0.61914999999999998</v>
       </c>
-      <c r="E112" s="4">
+      <c r="E112" s="5">
         <v>-0.38824999999999998</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="5">
         <v>0.54651000000000005</v>
       </c>
-      <c r="G112" s="4">
+      <c r="G112" s="5">
         <v>0.82982</v>
       </c>
-      <c r="H112" s="6">
+      <c r="H112" s="5">
         <v>-1.43011</v>
       </c>
-      <c r="I112" s="4">
+      <c r="I112" s="5">
         <v>-0.90895000000000004</v>
       </c>
-      <c r="J112" s="4">
+      <c r="J112" s="5">
         <v>0.42986999999999997</v>
       </c>
-      <c r="K112" s="4">
+      <c r="K112" s="5">
         <v>1.1923900000000001</v>
       </c>
-      <c r="L112" s="4">
+      <c r="L112" s="5">
         <v>-7.9450000000000007E-2</v>
       </c>
-      <c r="M112" s="4">
+      <c r="M112" s="5">
         <v>0.24632999999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A113" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B113" s="4">
+      <c r="B113" s="5">
         <v>-1.07514</v>
       </c>
-      <c r="C113" s="4">
+      <c r="C113" s="5">
         <v>1.5837699999999999</v>
       </c>
-      <c r="D113" s="4">
+      <c r="D113" s="5">
         <v>-1.1939200000000001</v>
       </c>
-      <c r="E113" s="4">
+      <c r="E113" s="5">
         <v>-1.0508299999999999</v>
       </c>
-      <c r="F113" s="4">
+      <c r="F113" s="5">
         <v>0.50926000000000005</v>
       </c>
-      <c r="G113" s="4">
+      <c r="G113" s="5">
         <v>0.58957999999999999</v>
       </c>
-      <c r="H113" s="6">
+      <c r="H113" s="5">
         <v>-1.7331700000000001</v>
       </c>
-      <c r="I113" s="4">
+      <c r="I113" s="5">
         <v>-0.61131999999999997</v>
       </c>
-      <c r="J113" s="4">
+      <c r="J113" s="5">
         <v>0.28408</v>
       </c>
-      <c r="K113" s="4">
+      <c r="K113" s="5">
         <v>1.8330200000000001</v>
       </c>
-      <c r="L113" s="4">
+      <c r="L113" s="5">
         <v>0.18901999999999999</v>
       </c>
-      <c r="M113" s="7">
+      <c r="M113" s="5">
         <v>3.9750400000000002E-4</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="5" t="s">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A114" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="5">
         <v>-0.92467999999999995</v>
       </c>
-      <c r="C114" s="4">
+      <c r="C114" s="5">
         <v>1.2345999999999999</v>
       </c>
-      <c r="D114" s="4">
+      <c r="D114" s="5">
         <v>-0.72799999999999998</v>
       </c>
-      <c r="E114" s="4">
+      <c r="E114" s="5">
         <v>-0.76420999999999994</v>
       </c>
-      <c r="F114" s="4">
+      <c r="F114" s="5">
         <v>0.32690999999999998</v>
       </c>
-      <c r="G114" s="4">
+      <c r="G114" s="5">
         <v>0.58043</v>
       </c>
-      <c r="H114" s="6">
+      <c r="H114" s="5">
         <v>-1.10219</v>
       </c>
-      <c r="I114" s="4">
+      <c r="I114" s="5">
         <v>-1.89242</v>
       </c>
-      <c r="J114" s="4">
+      <c r="J114" s="5">
         <v>0.10198</v>
       </c>
-      <c r="K114" s="4">
+      <c r="K114" s="5">
         <v>1.07043</v>
       </c>
-      <c r="L114" s="4">
+      <c r="L114" s="5">
         <v>5.7509999999999999E-2</v>
       </c>
-      <c r="M114" s="4">
+      <c r="M114" s="5">
         <v>-8.2400000000000008E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="5" t="s">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A115" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B115" s="4">
+      <c r="B115" s="5">
         <v>-0.89763999999999999</v>
       </c>
-      <c r="C115" s="4">
+      <c r="C115" s="5">
         <v>1.4993399999999999</v>
       </c>
-      <c r="D115" s="4">
+      <c r="D115" s="5">
         <v>-0.11915000000000001</v>
       </c>
-      <c r="E115" s="4">
+      <c r="E115" s="5">
         <v>-1.11771</v>
       </c>
-      <c r="F115" s="4">
+      <c r="F115" s="5">
         <v>0.47100999999999998</v>
       </c>
-      <c r="G115" s="4">
+      <c r="G115" s="5">
         <v>0.91364999999999996</v>
       </c>
-      <c r="H115" s="6">
+      <c r="H115" s="5">
         <v>-1.1083799999999999</v>
       </c>
-      <c r="I115" s="4">
+      <c r="I115" s="5">
         <v>-0.83572999999999997</v>
       </c>
-      <c r="J115" s="4">
+      <c r="J115" s="5">
         <v>0.12948999999999999</v>
       </c>
-      <c r="K115" s="4">
+      <c r="K115" s="5">
         <v>2.1390699999999998</v>
       </c>
-      <c r="L115" s="4">
+      <c r="L115" s="5">
         <v>0.22316</v>
       </c>
-      <c r="M115" s="4">
+      <c r="M115" s="5">
         <v>0.17680000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A116" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="5">
         <v>-1.08596</v>
       </c>
-      <c r="C116" s="4">
+      <c r="C116" s="5">
         <v>1.2603599999999999</v>
       </c>
-      <c r="D116" s="4">
+      <c r="D116" s="5">
         <v>-1.10737</v>
       </c>
-      <c r="E116" s="4">
+      <c r="E116" s="5">
         <v>-0.56662000000000001</v>
       </c>
-      <c r="F116" s="4">
+      <c r="F116" s="5">
         <v>0.62727999999999995</v>
       </c>
-      <c r="G116" s="4">
+      <c r="G116" s="5">
         <v>0.34486</v>
       </c>
-      <c r="H116" s="6">
+      <c r="H116" s="5">
         <v>-1.3041499999999999</v>
       </c>
-      <c r="I116" s="4">
+      <c r="I116" s="5">
         <v>-1.3949199999999999</v>
       </c>
-      <c r="J116" s="4">
+      <c r="J116" s="5">
         <v>0.22592999999999999</v>
       </c>
-      <c r="K116" s="4">
+      <c r="K116" s="5">
         <v>1.0075499999999999</v>
       </c>
-      <c r="L116" s="4">
+      <c r="L116" s="5">
         <v>-0.14366000000000001</v>
       </c>
-      <c r="M116" s="4">
+      <c r="M116" s="5">
         <v>-8.2970000000000002E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="5" t="s">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117" s="5">
         <v>-1.0546500000000001</v>
       </c>
-      <c r="C117" s="4">
+      <c r="C117" s="5">
         <v>1.1016900000000001</v>
       </c>
-      <c r="D117" s="4">
+      <c r="D117" s="5">
         <v>-0.84972000000000003</v>
       </c>
-      <c r="E117" s="4">
+      <c r="E117" s="5">
         <v>-1.06778</v>
       </c>
-      <c r="F117" s="4">
+      <c r="F117" s="5">
         <v>0.57403000000000004</v>
       </c>
-      <c r="G117" s="4">
+      <c r="G117" s="5">
         <v>0.61680000000000001</v>
       </c>
-      <c r="H117" s="6">
+      <c r="H117" s="5">
         <v>-1.0944199999999999</v>
       </c>
-      <c r="I117" s="4">
+      <c r="I117" s="5">
         <v>-0.42908000000000002</v>
       </c>
-      <c r="J117" s="4">
+      <c r="J117" s="5">
         <v>0.19757</v>
       </c>
-      <c r="K117" s="4">
+      <c r="K117" s="5">
         <v>2.0545499999999999</v>
       </c>
-      <c r="L117" s="4">
+      <c r="L117" s="5">
         <v>0.16688</v>
       </c>
-      <c r="M117" s="4">
+      <c r="M117" s="5">
         <v>0.12640999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="5" t="s">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="5">
         <v>-0.71247000000000005</v>
       </c>
-      <c r="C118" s="4">
+      <c r="C118" s="5">
         <v>1.0938300000000001</v>
       </c>
-      <c r="D118" s="4">
+      <c r="D118" s="5">
         <v>-9.8089999999999997E-2</v>
       </c>
-      <c r="E118" s="4">
+      <c r="E118" s="5">
         <v>-1.3434900000000001</v>
       </c>
-      <c r="F118" s="4">
+      <c r="F118" s="5">
         <v>-7.0430000000000006E-2</v>
       </c>
-      <c r="G118" s="4">
+      <c r="G118" s="5">
         <v>0.45745000000000002</v>
       </c>
-      <c r="H118" s="6">
+      <c r="H118" s="5">
         <v>-0.96462999999999999</v>
       </c>
-      <c r="I118" s="4">
+      <c r="I118" s="5">
         <v>7.5719999999999996E-2</v>
       </c>
-      <c r="J118" s="4">
+      <c r="J118" s="5">
         <v>0.44730999999999999</v>
       </c>
-      <c r="K118" s="4">
+      <c r="K118" s="5">
         <v>1.8070999999999999</v>
       </c>
-      <c r="L118" s="4">
+      <c r="L118" s="5">
         <v>0.45124999999999998</v>
       </c>
-      <c r="M118" s="4">
+      <c r="M118" s="5">
         <v>0.17660000000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="5" t="s">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119" s="5">
         <v>-0.87280999999999997</v>
       </c>
-      <c r="C119" s="4">
+      <c r="C119" s="5">
         <v>2.2119200000000001</v>
       </c>
-      <c r="D119" s="4">
+      <c r="D119" s="5">
         <v>-0.60909999999999997</v>
       </c>
-      <c r="E119" s="4">
+      <c r="E119" s="5">
         <v>-0.69018000000000002</v>
       </c>
-      <c r="F119" s="4">
+      <c r="F119" s="5">
         <v>0.65042999999999995</v>
       </c>
-      <c r="G119" s="4">
+      <c r="G119" s="5">
         <v>0.70631999999999995</v>
       </c>
-      <c r="H119" s="6">
+      <c r="H119" s="5">
         <v>-1.1612</v>
       </c>
-      <c r="I119" s="4">
+      <c r="I119" s="5">
         <v>-0.64598</v>
       </c>
-      <c r="J119" s="4">
+      <c r="J119" s="5">
         <v>0.17612</v>
       </c>
-      <c r="K119" s="4">
+      <c r="K119" s="5">
         <v>1.8828</v>
       </c>
-      <c r="L119" s="4">
+      <c r="L119" s="5">
         <v>0.20391999999999999</v>
       </c>
-      <c r="M119" s="4">
+      <c r="M119" s="5">
         <v>6.5269999999999995E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="5" t="s">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A120" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="5">
         <v>-1.0289200000000001</v>
       </c>
-      <c r="C120" s="4">
+      <c r="C120" s="5">
         <v>2.3278400000000001</v>
       </c>
-      <c r="D120" s="4">
+      <c r="D120" s="5">
         <v>-0.65620000000000001</v>
       </c>
-      <c r="E120" s="4">
+      <c r="E120" s="5">
         <v>-0.63734000000000002</v>
       </c>
-      <c r="F120" s="4">
+      <c r="F120" s="5">
         <v>0.48469000000000001</v>
       </c>
-      <c r="G120" s="4">
+      <c r="G120" s="5">
         <v>0.56686000000000003</v>
       </c>
-      <c r="H120" s="6">
+      <c r="H120" s="5">
         <v>-1.14391</v>
       </c>
-      <c r="I120" s="4">
+      <c r="I120" s="5">
         <v>-0.71696000000000004</v>
       </c>
-      <c r="J120" s="4">
+      <c r="J120" s="5">
         <v>0.16553999999999999</v>
       </c>
-      <c r="K120" s="4">
+      <c r="K120" s="5">
         <v>1.86547</v>
       </c>
-      <c r="L120" s="4">
+      <c r="L120" s="5">
         <v>1.389E-2</v>
       </c>
-      <c r="M120" s="4">
+      <c r="M120" s="5">
         <v>0.1802</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="5" t="s">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121" s="5">
         <v>-0.99160999999999999</v>
       </c>
-      <c r="C121" s="4">
+      <c r="C121" s="5">
         <v>1.7035499999999999</v>
       </c>
-      <c r="D121" s="4">
+      <c r="D121" s="5">
         <v>-0.80544000000000004</v>
       </c>
-      <c r="E121" s="4">
+      <c r="E121" s="5">
         <v>-0.77998000000000001</v>
       </c>
-      <c r="F121" s="4">
+      <c r="F121" s="5">
         <v>0.61629999999999996</v>
       </c>
-      <c r="G121" s="4">
+      <c r="G121" s="5">
         <v>0.57511999999999996</v>
       </c>
-      <c r="H121" s="6">
+      <c r="H121" s="5">
         <v>-1.10344</v>
       </c>
-      <c r="I121" s="4">
+      <c r="I121" s="5">
         <v>-0.53969</v>
       </c>
-      <c r="J121" s="4">
+      <c r="J121" s="5">
         <v>0.16087000000000001</v>
       </c>
-      <c r="K121" s="4">
+      <c r="K121" s="5">
         <v>1.57847</v>
       </c>
-      <c r="L121" s="4">
+      <c r="L121" s="5">
         <v>-5.3099999999999996E-3</v>
       </c>
-      <c r="M121" s="4">
+      <c r="M121" s="5">
         <v>3.1230000000000001E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="5" t="s">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A122" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="5">
         <v>-1.3285100000000001</v>
       </c>
-      <c r="C122" s="4">
+      <c r="C122" s="5">
         <v>1.58196</v>
       </c>
-      <c r="D122" s="4">
+      <c r="D122" s="5">
         <v>-0.75519000000000003</v>
       </c>
-      <c r="E122" s="4">
+      <c r="E122" s="5">
         <v>-0.63107000000000002</v>
       </c>
-      <c r="F122" s="4">
+      <c r="F122" s="5">
         <v>0.31308999999999998</v>
       </c>
-      <c r="G122" s="4">
+      <c r="G122" s="5">
         <v>0.39372000000000001</v>
       </c>
-      <c r="H122" s="6">
+      <c r="H122" s="5">
         <v>-1.5029300000000001</v>
       </c>
-      <c r="I122" s="4">
+      <c r="I122" s="5">
         <v>-1.5607899999999999</v>
       </c>
-      <c r="J122" s="4">
+      <c r="J122" s="5">
         <v>0.15187999999999999</v>
       </c>
-      <c r="K122" s="4">
+      <c r="K122" s="5">
         <v>1.25125</v>
       </c>
-      <c r="L122" s="4">
+      <c r="L122" s="5">
         <v>-8.8160000000000002E-2</v>
       </c>
-      <c r="M122" s="4">
+      <c r="M122" s="5">
         <v>-0.11311</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="5" t="s">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123" s="5">
         <v>-1.2311000000000001</v>
       </c>
-      <c r="C123" s="4">
+      <c r="C123" s="5">
         <v>1.15306</v>
       </c>
-      <c r="D123" s="4">
+      <c r="D123" s="5">
         <v>-0.90417000000000003</v>
       </c>
-      <c r="E123" s="4">
+      <c r="E123" s="5">
         <v>-1.14998</v>
       </c>
-      <c r="F123" s="4">
+      <c r="F123" s="5">
         <v>0.39366000000000001</v>
       </c>
-      <c r="G123" s="4">
+      <c r="G123" s="5">
         <v>0.10319</v>
       </c>
-      <c r="H123" s="6">
+      <c r="H123" s="5">
         <v>-1.20326</v>
       </c>
-      <c r="I123" s="4">
+      <c r="I123" s="5">
         <v>-0.92942000000000002</v>
       </c>
-      <c r="J123" s="4">
+      <c r="J123" s="5">
         <v>0.31734000000000001</v>
       </c>
-      <c r="K123" s="4">
+      <c r="K123" s="5">
         <v>2.4056000000000002</v>
       </c>
-      <c r="L123" s="4">
+      <c r="L123" s="5">
         <v>1.478E-2</v>
       </c>
-      <c r="M123" s="4">
+      <c r="M123" s="5">
         <v>7.5939999999999994E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="5" t="s">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A124" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="5">
         <v>-1.2001299999999999</v>
       </c>
-      <c r="C124" s="4">
+      <c r="C124" s="5">
         <v>1.11839</v>
       </c>
-      <c r="D124" s="4">
+      <c r="D124" s="5">
         <v>-1.03348</v>
       </c>
-      <c r="E124" s="4">
+      <c r="E124" s="5">
         <v>-1.11063</v>
       </c>
-      <c r="F124" s="4">
+      <c r="F124" s="5">
         <v>0.54481000000000002</v>
       </c>
-      <c r="G124" s="4">
+      <c r="G124" s="5">
         <v>0.40538000000000002</v>
       </c>
-      <c r="H124" s="6">
+      <c r="H124" s="5">
         <v>-1.5470699999999999</v>
       </c>
-      <c r="I124" s="4">
+      <c r="I124" s="5">
         <v>-1.23533</v>
       </c>
-      <c r="J124" s="4">
+      <c r="J124" s="5">
         <v>0.15293000000000001</v>
       </c>
-      <c r="K124" s="4">
+      <c r="K124" s="5">
         <v>2.1987199999999998</v>
       </c>
-      <c r="L124" s="4">
+      <c r="L124" s="5">
         <v>-0.28239999999999998</v>
       </c>
-      <c r="M124" s="4">
+      <c r="M124" s="5">
         <v>2.97E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="5" t="s">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A125" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125" s="5">
         <v>-0.82138999999999995</v>
       </c>
-      <c r="C125" s="4">
+      <c r="C125" s="5">
         <v>2.0458099999999999</v>
       </c>
-      <c r="D125" s="4">
+      <c r="D125" s="5">
         <v>-0.64651999999999998</v>
       </c>
-      <c r="E125" s="4">
+      <c r="E125" s="5">
         <v>-0.41519</v>
       </c>
-      <c r="F125" s="4">
+      <c r="F125" s="5">
         <v>0.51768000000000003</v>
       </c>
-      <c r="G125" s="4">
+      <c r="G125" s="5">
         <v>1.1119300000000001</v>
       </c>
-      <c r="H125" s="6">
+      <c r="H125" s="5">
         <v>-0.93627000000000005</v>
       </c>
-      <c r="I125" s="4">
+      <c r="I125" s="5">
         <v>-1.2452399999999999</v>
       </c>
-      <c r="J125" s="4">
+      <c r="J125" s="5">
         <v>0.11962</v>
       </c>
-      <c r="K125" s="4">
+      <c r="K125" s="5">
         <v>0.71633000000000002</v>
       </c>
-      <c r="L125" s="4">
+      <c r="L125" s="5">
         <v>0.26016</v>
       </c>
-      <c r="M125" s="4">
+      <c r="M125" s="5">
         <v>0.12217</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="5" t="s">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A126" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="5">
         <v>-0.64963000000000004</v>
       </c>
-      <c r="C126" s="4">
+      <c r="C126" s="5">
         <v>1.9219599999999999</v>
       </c>
-      <c r="D126" s="4">
+      <c r="D126" s="5">
         <v>-0.77237999999999996</v>
       </c>
-      <c r="E126" s="4">
+      <c r="E126" s="5">
         <v>-0.14152000000000001</v>
       </c>
-      <c r="F126" s="4">
+      <c r="F126" s="5">
         <v>0.69515000000000005</v>
       </c>
-      <c r="G126" s="4">
+      <c r="G126" s="5">
         <v>0.90417999999999998</v>
       </c>
-      <c r="H126" s="6">
+      <c r="H126" s="5">
         <v>-0.91156000000000004</v>
       </c>
-      <c r="I126" s="4">
+      <c r="I126" s="5">
         <v>-1.5380499999999999</v>
       </c>
-      <c r="J126" s="4">
+      <c r="J126" s="5">
         <v>6.7309999999999995E-2</v>
       </c>
-      <c r="K126" s="4">
+      <c r="K126" s="5">
         <v>0.88119000000000003</v>
       </c>
-      <c r="L126" s="4">
+      <c r="L126" s="5">
         <v>5.5140000000000002E-2</v>
       </c>
-      <c r="M126" s="4">
+      <c r="M126" s="5">
         <v>2.6009999999999998E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="5" t="s">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B127" s="4">
+      <c r="B127" s="5">
         <v>-1.2384500000000001</v>
       </c>
-      <c r="C127" s="4">
+      <c r="C127" s="5">
         <v>0.78942000000000001</v>
       </c>
-      <c r="D127" s="4">
+      <c r="D127" s="5">
         <v>-1.12053</v>
       </c>
-      <c r="E127" s="4">
+      <c r="E127" s="5">
         <v>-1.05284</v>
       </c>
-      <c r="F127" s="4">
+      <c r="F127" s="5">
         <v>0.40405000000000002</v>
       </c>
-      <c r="G127" s="4">
+      <c r="G127" s="5">
         <v>0.34589999999999999</v>
       </c>
-      <c r="H127" s="6">
+      <c r="H127" s="5">
         <v>-1.19059</v>
       </c>
-      <c r="I127" s="4">
+      <c r="I127" s="5">
         <v>-1.51637</v>
       </c>
-      <c r="J127" s="4">
+      <c r="J127" s="5">
         <v>2.375E-2</v>
       </c>
-      <c r="K127" s="4">
+      <c r="K127" s="5">
         <v>1.5429999999999999</v>
       </c>
-      <c r="L127" s="4">
+      <c r="L127" s="5">
         <v>-2.8469999999999999E-2</v>
       </c>
-      <c r="M127" s="4">
+      <c r="M127" s="5">
         <v>3.4459999999999998E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="5" t="s">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="5">
         <v>-1.11273</v>
       </c>
-      <c r="C128" s="4">
+      <c r="C128" s="5">
         <v>1.1352100000000001</v>
       </c>
-      <c r="D128" s="4">
+      <c r="D128" s="5">
         <v>-1.15838</v>
       </c>
-      <c r="E128" s="4">
+      <c r="E128" s="5">
         <v>-1.03823</v>
       </c>
-      <c r="F128" s="4">
+      <c r="F128" s="5">
         <v>0.59150000000000003</v>
       </c>
-      <c r="G128" s="4">
+      <c r="G128" s="5">
         <v>0.51978000000000002</v>
       </c>
-      <c r="H128" s="6">
+      <c r="H128" s="5">
         <v>-1.1856199999999999</v>
       </c>
-      <c r="I128" s="4">
+      <c r="I128" s="5">
         <v>-0.63349</v>
       </c>
-      <c r="J128" s="4">
+      <c r="J128" s="5">
         <v>5.1679999999999997E-2</v>
       </c>
-      <c r="K128" s="4">
+      <c r="K128" s="5">
         <v>2.06169</v>
       </c>
-      <c r="L128" s="4">
+      <c r="L128" s="5">
         <v>0.17624999999999999</v>
       </c>
-      <c r="M128" s="4">
+      <c r="M128" s="5">
         <v>-5.4850000000000003E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B129" s="4">
+      <c r="B129" s="5">
         <v>-0.95638000000000001</v>
       </c>
-      <c r="C129" s="4">
+      <c r="C129" s="5">
         <v>2.2388599999999999</v>
       </c>
-      <c r="D129" s="4">
+      <c r="D129" s="5">
         <v>-0.58553999999999995</v>
       </c>
-      <c r="E129" s="4">
+      <c r="E129" s="5">
         <v>-0.89868999999999999</v>
       </c>
-      <c r="F129" s="4">
+      <c r="F129" s="5">
         <v>0.5736</v>
       </c>
-      <c r="G129" s="4">
+      <c r="G129" s="5">
         <v>1.05718</v>
       </c>
-      <c r="H129" s="6">
+      <c r="H129" s="5">
         <v>-1.04878</v>
       </c>
-      <c r="I129" s="4">
+      <c r="I129" s="5">
         <v>-1.0947899999999999</v>
       </c>
-      <c r="J129" s="4">
+      <c r="J129" s="5">
         <v>-9.572E-2</v>
       </c>
-      <c r="K129" s="4">
+      <c r="K129" s="5">
         <v>2.0872199999999999</v>
       </c>
-      <c r="L129" s="4">
+      <c r="L129" s="5">
         <v>6.6809999999999994E-2</v>
       </c>
-      <c r="M129" s="4">
+      <c r="M129" s="5">
         <v>6.3729999999999995E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A130" s="5" t="s">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="5">
         <v>-0.92774999999999996</v>
       </c>
-      <c r="C130" s="4">
+      <c r="C130" s="5">
         <v>1.9510099999999999</v>
       </c>
-      <c r="D130" s="4">
+      <c r="D130" s="5">
         <v>-0.84309000000000001</v>
       </c>
-      <c r="E130" s="4">
+      <c r="E130" s="5">
         <v>-0.67352999999999996</v>
       </c>
-      <c r="F130" s="4">
+      <c r="F130" s="5">
         <v>0.63751000000000002</v>
       </c>
-      <c r="G130" s="4">
+      <c r="G130" s="5">
         <v>0.81089999999999995</v>
       </c>
-      <c r="H130" s="6">
+      <c r="H130" s="5">
         <v>-1.0321100000000001</v>
       </c>
-      <c r="I130" s="4">
+      <c r="I130" s="5">
         <v>-1.00282</v>
       </c>
-      <c r="J130" s="4">
+      <c r="J130" s="5">
         <v>4.0969999999999999E-2</v>
       </c>
-      <c r="K130" s="4">
+      <c r="K130" s="5">
         <v>1.7622599999999999</v>
       </c>
-      <c r="L130" s="4">
+      <c r="L130" s="5">
         <v>1.456E-2</v>
       </c>
-      <c r="M130" s="4">
+      <c r="M130" s="5">
         <v>0.10229000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="5" t="s">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B131" s="4">
+      <c r="B131" s="5">
         <v>-1.2461899999999999</v>
       </c>
-      <c r="C131" s="4">
+      <c r="C131" s="5">
         <v>1.8324199999999999</v>
       </c>
-      <c r="D131" s="4">
+      <c r="D131" s="5">
         <v>-0.24787000000000001</v>
       </c>
-      <c r="E131" s="4">
+      <c r="E131" s="5">
         <v>-0.97643000000000002</v>
       </c>
-      <c r="F131" s="4">
+      <c r="F131" s="5">
         <v>0.36130000000000001</v>
       </c>
-      <c r="G131" s="4">
+      <c r="G131" s="5">
         <v>0.1913</v>
       </c>
-      <c r="H131" s="6">
+      <c r="H131" s="5">
         <v>-1.3326</v>
       </c>
-      <c r="I131" s="4">
+      <c r="I131" s="5">
         <v>-0.45254</v>
       </c>
-      <c r="J131" s="4">
+      <c r="J131" s="5">
         <v>8.1920000000000007E-2</v>
       </c>
-      <c r="K131" s="4">
+      <c r="K131" s="5">
         <v>2.2929400000000002</v>
       </c>
-      <c r="L131" s="4">
+      <c r="L131" s="5">
         <v>3.066E-2</v>
       </c>
-      <c r="M131" s="4">
+      <c r="M131" s="5">
         <v>-2.6720000000000001E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A132" s="5" t="s">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="5">
         <v>-1.19502</v>
       </c>
-      <c r="C132" s="4">
+      <c r="C132" s="5">
         <v>1.5650200000000001</v>
       </c>
-      <c r="D132" s="4">
+      <c r="D132" s="5">
         <v>-0.97894999999999999</v>
       </c>
-      <c r="E132" s="4">
+      <c r="E132" s="5">
         <v>-0.90730999999999995</v>
       </c>
-      <c r="F132" s="4">
+      <c r="F132" s="5">
         <v>0.57852000000000003</v>
       </c>
-      <c r="G132" s="4">
+      <c r="G132" s="5">
         <v>0.43530999999999997</v>
       </c>
-      <c r="H132" s="6">
+      <c r="H132" s="5">
         <v>-1.50112</v>
       </c>
-      <c r="I132" s="4">
+      <c r="I132" s="5">
         <v>-0.92703000000000002</v>
       </c>
-      <c r="J132" s="4">
+      <c r="J132" s="5">
         <v>0.24279000000000001</v>
       </c>
-      <c r="K132" s="4">
+      <c r="K132" s="5">
         <v>2.0873400000000002</v>
       </c>
-      <c r="L132" s="4">
+      <c r="L132" s="5">
         <v>-0.16705</v>
       </c>
-      <c r="M132" s="4">
+      <c r="M132" s="5">
         <v>-8.9480000000000004E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="5" t="s">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133" s="5">
         <v>-1.2145600000000001</v>
       </c>
-      <c r="C133" s="4">
+      <c r="C133" s="5">
         <v>1.39238</v>
       </c>
-      <c r="D133" s="4">
+      <c r="D133" s="5">
         <v>-0.24811</v>
       </c>
-      <c r="E133" s="4">
+      <c r="E133" s="5">
         <v>-1.2651300000000001</v>
       </c>
-      <c r="F133" s="4">
+      <c r="F133" s="5">
         <v>0.38168000000000002</v>
       </c>
-      <c r="G133" s="4">
+      <c r="G133" s="5">
         <v>0.46088000000000001</v>
       </c>
-      <c r="H133" s="6">
+      <c r="H133" s="5">
         <v>-1.3118099999999999</v>
       </c>
-      <c r="I133" s="4">
+      <c r="I133" s="5">
         <v>-0.25413999999999998</v>
       </c>
-      <c r="J133" s="4">
+      <c r="J133" s="5">
         <v>0.14155999999999999</v>
       </c>
-      <c r="K133" s="4">
+      <c r="K133" s="5">
         <v>2.4623699999999999</v>
       </c>
-      <c r="L133" s="4">
+      <c r="L133" s="5">
         <v>-0.14374000000000001</v>
       </c>
-      <c r="M133" s="4">
+      <c r="M133" s="5">
         <v>0.13755000000000001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="5" t="s">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="5">
         <v>-0.76980000000000004</v>
       </c>
-      <c r="C134" s="4">
+      <c r="C134" s="5">
         <v>1.9910699999999999</v>
       </c>
-      <c r="D134" s="4">
+      <c r="D134" s="5">
         <v>-5.457E-2</v>
       </c>
-      <c r="E134" s="4">
+      <c r="E134" s="5">
         <v>-0.86770000000000003</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="5">
         <v>0.68771000000000004</v>
       </c>
-      <c r="G134" s="4">
+      <c r="G134" s="5">
         <v>0.77388000000000001</v>
       </c>
-      <c r="H134" s="6">
+      <c r="H134" s="5">
         <v>-0.95525000000000004</v>
       </c>
-      <c r="I134" s="4">
+      <c r="I134" s="5">
         <v>-0.55393999999999999</v>
       </c>
-      <c r="J134" s="4">
+      <c r="J134" s="5">
         <v>0.22883000000000001</v>
       </c>
-      <c r="K134" s="4">
+      <c r="K134" s="5">
         <v>2.1940900000000001</v>
       </c>
-      <c r="L134" s="4">
+      <c r="L134" s="5">
         <v>-0.28420000000000001</v>
       </c>
-      <c r="M134" s="4">
+      <c r="M134" s="5">
         <v>-0.12414</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A135" s="5" t="s">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B135" s="4">
+      <c r="B135" s="5">
         <v>-0.92723</v>
       </c>
-      <c r="C135" s="4">
+      <c r="C135" s="5">
         <v>1.7353099999999999</v>
       </c>
-      <c r="D135" s="4">
+      <c r="D135" s="5">
         <v>-8.6529999999999996E-2</v>
       </c>
-      <c r="E135" s="4">
+      <c r="E135" s="5">
         <v>-0.50058000000000002</v>
       </c>
-      <c r="F135" s="4">
+      <c r="F135" s="5">
         <v>0.65112999999999999</v>
       </c>
-      <c r="G135" s="4">
+      <c r="G135" s="5">
         <v>0.56022000000000005</v>
       </c>
-      <c r="H135" s="6">
+      <c r="H135" s="5">
         <v>-1.2269300000000001</v>
       </c>
-      <c r="I135" s="4">
+      <c r="I135" s="5">
         <v>-0.52825</v>
       </c>
-      <c r="J135" s="4">
+      <c r="J135" s="5">
         <v>0.16769000000000001</v>
       </c>
-      <c r="K135" s="4">
+      <c r="K135" s="5">
         <v>0.73528000000000004</v>
       </c>
-      <c r="L135" s="4">
+      <c r="L135" s="5">
         <v>9.11E-2</v>
       </c>
-      <c r="M135" s="4">
+      <c r="M135" s="5">
         <v>0.11898</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A136" s="5" t="s">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="5">
         <v>-1.0650299999999999</v>
       </c>
-      <c r="C136" s="4">
+      <c r="C136" s="5">
         <v>1.95644</v>
       </c>
-      <c r="D136" s="4">
+      <c r="D136" s="5">
         <v>-0.86643000000000003</v>
       </c>
-      <c r="E136" s="4">
+      <c r="E136" s="5">
         <v>-0.76576</v>
       </c>
-      <c r="F136" s="4">
+      <c r="F136" s="5">
         <v>0.48141</v>
       </c>
-      <c r="G136" s="4">
+      <c r="G136" s="5">
         <v>0.58306000000000002</v>
       </c>
-      <c r="H136" s="6">
+      <c r="H136" s="5">
         <v>-1.3859399999999999</v>
       </c>
-      <c r="I136" s="4">
+      <c r="I136" s="5">
         <v>-2.2852000000000001</v>
       </c>
-      <c r="J136" s="4">
+      <c r="J136" s="5">
         <v>7.9439999999999997E-2</v>
       </c>
-      <c r="K136" s="4">
+      <c r="K136" s="5">
         <v>2.1285500000000002</v>
       </c>
-      <c r="L136" s="4">
+      <c r="L136" s="5">
         <v>-8.949E-2</v>
       </c>
-      <c r="M136" s="4">
+      <c r="M136" s="5">
         <v>-6.3420000000000004E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A137" s="5" t="s">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B137" s="4">
+      <c r="B137" s="5">
         <v>-1.1174500000000001</v>
       </c>
-      <c r="C137" s="4">
+      <c r="C137" s="5">
         <v>1.32803</v>
       </c>
-      <c r="D137" s="4">
+      <c r="D137" s="5">
         <v>-0.62890000000000001</v>
       </c>
-      <c r="E137" s="4">
+      <c r="E137" s="5">
         <v>-1.1772100000000001</v>
       </c>
-      <c r="F137" s="4">
+      <c r="F137" s="5">
         <v>0.79349000000000003</v>
       </c>
-      <c r="G137" s="4">
+      <c r="G137" s="5">
         <v>0.56855</v>
       </c>
-      <c r="H137" s="6">
+      <c r="H137" s="5">
         <v>-1.10873</v>
       </c>
-      <c r="I137" s="4">
+      <c r="I137" s="5">
         <v>-0.58065999999999995</v>
       </c>
-      <c r="J137" s="4">
+      <c r="J137" s="5">
         <v>3.46E-3</v>
       </c>
-      <c r="K137" s="4">
+      <c r="K137" s="5">
         <v>2.2448600000000001</v>
       </c>
-      <c r="L137" s="4">
+      <c r="L137" s="5">
         <v>0.28354000000000001</v>
       </c>
-      <c r="M137" s="4">
+      <c r="M137" s="5">
         <v>2.7799999999999998E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A138" s="5" t="s">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="5">
         <v>-0.82984000000000002</v>
       </c>
-      <c r="C138" s="4">
+      <c r="C138" s="5">
         <v>1.48464</v>
       </c>
-      <c r="D138" s="4">
+      <c r="D138" s="5">
         <v>-0.81593000000000004</v>
       </c>
-      <c r="E138" s="4">
+      <c r="E138" s="5">
         <v>-0.50805999999999996</v>
       </c>
-      <c r="F138" s="4">
+      <c r="F138" s="5">
         <v>0.39137</v>
       </c>
-      <c r="G138" s="4">
+      <c r="G138" s="5">
         <v>0.60280999999999996</v>
       </c>
-      <c r="H138" s="6">
+      <c r="H138" s="5">
         <v>-0.56089999999999995</v>
       </c>
-      <c r="I138" s="4">
+      <c r="I138" s="5">
         <v>-0.71994000000000002</v>
       </c>
-      <c r="J138" s="4">
+      <c r="J138" s="5">
         <v>0.13988</v>
       </c>
-      <c r="K138" s="4">
+      <c r="K138" s="5">
         <v>0.88915999999999995</v>
       </c>
-      <c r="L138" s="4">
+      <c r="L138" s="5">
         <v>-1.487E-2</v>
       </c>
-      <c r="M138" s="4">
+      <c r="M138" s="5">
         <v>-2.4279999999999999E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A139" s="5" t="s">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B139" s="4">
+      <c r="B139" s="5">
         <v>-1.3557699999999999</v>
       </c>
-      <c r="C139" s="4">
+      <c r="C139" s="5">
         <v>1.09551</v>
       </c>
-      <c r="D139" s="4">
+      <c r="D139" s="5">
         <v>-1.03013</v>
       </c>
-      <c r="E139" s="4">
+      <c r="E139" s="5">
         <v>-1.05087</v>
       </c>
-      <c r="F139" s="4">
+      <c r="F139" s="5">
         <v>0.39244000000000001</v>
       </c>
-      <c r="G139" s="4">
+      <c r="G139" s="5">
         <v>0.38145000000000001</v>
       </c>
-      <c r="H139" s="6">
+      <c r="H139" s="5">
         <v>-1.4721500000000001</v>
       </c>
-      <c r="I139" s="4">
+      <c r="I139" s="5">
         <v>-0.72306999999999999</v>
       </c>
-      <c r="J139" s="4">
+      <c r="J139" s="5">
         <v>5.4679999999999999E-2</v>
       </c>
-      <c r="K139" s="4">
+      <c r="K139" s="5">
         <v>1.19191</v>
       </c>
-      <c r="L139" s="4">
+      <c r="L139" s="5">
         <v>0.20435</v>
       </c>
-      <c r="M139" s="4">
+      <c r="M139" s="5">
         <v>-0.13045000000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A140" s="5" t="s">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A140" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140" s="5">
         <v>-1.11938</v>
       </c>
-      <c r="C140" s="4">
+      <c r="C140" s="5">
         <v>1.28935</v>
       </c>
-      <c r="D140" s="4">
+      <c r="D140" s="5">
         <v>-1.3398699999999999</v>
       </c>
-      <c r="E140" s="4">
+      <c r="E140" s="5">
         <v>-0.86712999999999996</v>
       </c>
-      <c r="F140" s="4">
+      <c r="F140" s="5">
         <v>0.68701000000000001</v>
       </c>
-      <c r="G140" s="4">
+      <c r="G140" s="5">
         <v>0.76351000000000002</v>
       </c>
-      <c r="H140" s="6">
+      <c r="H140" s="5">
         <v>-1.2144200000000001</v>
       </c>
-      <c r="I140" s="4">
+      <c r="I140" s="5">
         <v>-1.70852</v>
       </c>
-      <c r="J140" s="4">
+      <c r="J140" s="5">
         <v>8.5080000000000003E-2</v>
       </c>
-      <c r="K140" s="4">
+      <c r="K140" s="5">
         <v>1.46932</v>
       </c>
-      <c r="L140" s="4">
+      <c r="L140" s="5">
         <v>0.19234999999999999</v>
       </c>
-      <c r="M140" s="4">
+      <c r="M140" s="5">
         <v>-5.2659999999999998E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A141" s="5" t="s">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A141" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B141" s="4">
+      <c r="B141" s="5">
         <v>-1.4788699999999999</v>
       </c>
-      <c r="C141" s="4">
+      <c r="C141" s="5">
         <v>0.56611999999999996</v>
       </c>
-      <c r="D141" s="4">
+      <c r="D141" s="5">
         <v>-1.30498</v>
       </c>
-      <c r="E141" s="4">
+      <c r="E141" s="5">
         <v>-1.262</v>
       </c>
-      <c r="F141" s="4">
+      <c r="F141" s="5">
         <v>7.7890000000000001E-2</v>
       </c>
-      <c r="G141" s="4">
+      <c r="G141" s="5">
         <v>7.6079999999999995E-2</v>
       </c>
-      <c r="H141" s="6">
+      <c r="H141" s="5">
         <v>-1.26105</v>
       </c>
-      <c r="I141" s="4">
+      <c r="I141" s="5">
         <v>-0.29887999999999998</v>
       </c>
-      <c r="J141" s="4">
+      <c r="J141" s="5">
         <v>0.11534</v>
       </c>
-      <c r="K141" s="4">
+      <c r="K141" s="5">
         <v>1.5279100000000001</v>
       </c>
-      <c r="L141" s="4">
+      <c r="L141" s="5">
         <v>-5.0299999999999997E-2</v>
       </c>
-      <c r="M141" s="4">
+      <c r="M141" s="5">
         <v>-8.5319999999999993E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A142" s="5" t="s">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A142" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142" s="5">
         <v>-1.2703100000000001</v>
       </c>
-      <c r="C142" s="4">
+      <c r="C142" s="5">
         <v>1.71732</v>
       </c>
-      <c r="D142" s="4">
+      <c r="D142" s="5">
         <v>-0.75741000000000003</v>
       </c>
-      <c r="E142" s="4">
+      <c r="E142" s="5">
         <v>-0.99268999999999996</v>
       </c>
-      <c r="F142" s="4">
+      <c r="F142" s="5">
         <v>0.59318000000000004</v>
       </c>
-      <c r="G142" s="4">
+      <c r="G142" s="5">
         <v>0.68771000000000004</v>
       </c>
-      <c r="H142" s="6">
+      <c r="H142" s="5">
         <v>-1.04905</v>
       </c>
-      <c r="I142" s="4">
+      <c r="I142" s="5">
         <v>-0.40899999999999997</v>
       </c>
-      <c r="J142" s="4">
+      <c r="J142" s="5">
         <v>1.5440000000000001E-2</v>
       </c>
-      <c r="K142" s="4">
+      <c r="K142" s="5">
         <v>1.92137</v>
       </c>
-      <c r="L142" s="4">
+      <c r="L142" s="5">
         <v>2.0580000000000001E-2</v>
       </c>
-      <c r="M142" s="4">
+      <c r="M142" s="5">
         <v>6.6669999999999993E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A143" s="5" t="s">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A143" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B143" s="4">
+      <c r="B143" s="5">
         <v>-1.1490400000000001</v>
       </c>
-      <c r="C143" s="4">
+      <c r="C143" s="5">
         <v>2.0176799999999999</v>
       </c>
-      <c r="D143" s="4">
+      <c r="D143" s="5">
         <v>-0.51153999999999999</v>
       </c>
-      <c r="E143" s="4">
+      <c r="E143" s="5">
         <v>-0.65747999999999995</v>
       </c>
-      <c r="F143" s="4">
+      <c r="F143" s="5">
         <v>0.46581</v>
       </c>
-      <c r="G143" s="4">
+      <c r="G143" s="5">
         <v>0.46703</v>
       </c>
-      <c r="H143" s="6">
+      <c r="H143" s="5">
         <v>-1.02166</v>
       </c>
-      <c r="I143" s="4">
+      <c r="I143" s="5">
         <v>-0.55003000000000002</v>
       </c>
-      <c r="J143" s="4">
+      <c r="J143" s="5">
         <v>0.10706</v>
       </c>
-      <c r="K143" s="4">
+      <c r="K143" s="5">
         <v>1.6839999999999999</v>
       </c>
-      <c r="L143" s="4">
+      <c r="L143" s="5">
         <v>4.8320000000000002E-2</v>
       </c>
-      <c r="M143" s="4">
+      <c r="M143" s="5">
         <v>0.14882000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A144" s="5" t="s">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A144" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144" s="5">
         <v>-1.0389600000000001</v>
       </c>
-      <c r="C144" s="4">
+      <c r="C144" s="5">
         <v>1.5467200000000001</v>
       </c>
-      <c r="D144" s="4">
+      <c r="D144" s="5">
         <v>-0.74046000000000001</v>
       </c>
-      <c r="E144" s="4">
+      <c r="E144" s="5">
         <v>-0.85377999999999998</v>
       </c>
-      <c r="F144" s="4">
+      <c r="F144" s="5">
         <v>0.53713</v>
       </c>
-      <c r="G144" s="4">
+      <c r="G144" s="5">
         <v>0.54213999999999996</v>
       </c>
-      <c r="H144" s="6">
+      <c r="H144" s="5">
         <v>-1.18241</v>
       </c>
-      <c r="I144" s="4">
+      <c r="I144" s="5">
         <v>-0.77405000000000002</v>
       </c>
-      <c r="J144" s="4">
+      <c r="J144" s="5">
         <v>0.13070999999999999</v>
       </c>
-      <c r="K144" s="4">
+      <c r="K144" s="5">
         <v>2.0320399999999998</v>
       </c>
-      <c r="L144" s="4">
+      <c r="L144" s="5">
         <v>2.9260000000000001E-2</v>
       </c>
-      <c r="M144" s="4">
+      <c r="M144" s="5">
         <v>0.11720999999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A145" s="5" t="s">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A145" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B145" s="4">
+      <c r="B145" s="5">
         <v>-1.0233099999999999</v>
       </c>
-      <c r="C145" s="4">
+      <c r="C145" s="5">
         <v>1.67971</v>
       </c>
-      <c r="D145" s="4">
+      <c r="D145" s="5">
         <v>-0.50368000000000002</v>
       </c>
-      <c r="E145" s="4">
+      <c r="E145" s="5">
         <v>-0.91849000000000003</v>
       </c>
-      <c r="F145" s="4">
+      <c r="F145" s="5">
         <v>0.40153</v>
       </c>
-      <c r="G145" s="4">
+      <c r="G145" s="5">
         <v>0.64505000000000001</v>
       </c>
-      <c r="H145" s="6">
+      <c r="H145" s="5">
         <v>-1.0844499999999999</v>
       </c>
-      <c r="I145" s="4">
+      <c r="I145" s="5">
         <v>-0.66829000000000005</v>
       </c>
-      <c r="J145" s="4">
+      <c r="J145" s="5">
         <v>8.4900000000000003E-2</v>
       </c>
-      <c r="K145" s="4">
+      <c r="K145" s="5">
         <v>2.26715</v>
       </c>
-      <c r="L145" s="4">
+      <c r="L145" s="5">
         <v>2.6540000000000001E-2</v>
       </c>
-      <c r="M145" s="4">
+      <c r="M145" s="5">
         <v>6.9360000000000005E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A146" s="5" t="s">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A146" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="5">
         <v>-1.02613</v>
       </c>
-      <c r="C146" s="4">
+      <c r="C146" s="5">
         <v>1.8043800000000001</v>
       </c>
-      <c r="D146" s="4">
+      <c r="D146" s="5">
         <v>-0.53581999999999996</v>
       </c>
-      <c r="E146" s="4">
+      <c r="E146" s="5">
         <v>-0.91744000000000003</v>
       </c>
-      <c r="F146" s="4">
+      <c r="F146" s="5">
         <v>0.37025000000000002</v>
       </c>
-      <c r="G146" s="4">
+      <c r="G146" s="5">
         <v>0.69282999999999995</v>
       </c>
-      <c r="H146" s="6">
+      <c r="H146" s="5">
         <v>-1.2099800000000001</v>
       </c>
-      <c r="I146" s="4">
+      <c r="I146" s="5">
         <v>-0.47610000000000002</v>
       </c>
-      <c r="J146" s="4">
+      <c r="J146" s="5">
         <v>-2.6540000000000001E-2</v>
       </c>
-      <c r="K146" s="4">
+      <c r="K146" s="5">
         <v>2.66534</v>
       </c>
-      <c r="L146" s="4">
+      <c r="L146" s="5">
         <v>0.17024</v>
       </c>
-      <c r="M146" s="4">
+      <c r="M146" s="5">
         <v>9.0740000000000001E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A147" s="5" t="s">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A147" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B147" s="5">
         <v>-1.0631999999999999</v>
       </c>
-      <c r="C147" s="4">
+      <c r="C147" s="5">
         <v>1.42469</v>
       </c>
-      <c r="D147" s="4">
+      <c r="D147" s="5">
         <v>-0.75</v>
       </c>
-      <c r="E147" s="4">
+      <c r="E147" s="5">
         <v>-0.79783000000000004</v>
       </c>
-      <c r="F147" s="4">
+      <c r="F147" s="5">
         <v>0.58337000000000006</v>
       </c>
-      <c r="G147" s="4">
+      <c r="G147" s="5">
         <v>0.73767000000000005</v>
       </c>
-      <c r="H147" s="6">
+      <c r="H147" s="5">
         <v>-1.0321</v>
       </c>
-      <c r="I147" s="4">
+      <c r="I147" s="5">
         <v>-0.79259000000000002</v>
       </c>
-      <c r="J147" s="4">
+      <c r="J147" s="5">
         <v>4.4600000000000004E-3</v>
       </c>
-      <c r="K147" s="4">
+      <c r="K147" s="5">
         <v>1.74088</v>
       </c>
-      <c r="L147" s="4">
+      <c r="L147" s="5">
         <v>-1.8859999999999998E-2</v>
       </c>
-      <c r="M147" s="4">
+      <c r="M147" s="5">
         <v>3.6670000000000001E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A148" s="5" t="s">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A148" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148" s="5">
         <v>-0.92886999999999997</v>
       </c>
-      <c r="C148" s="4">
+      <c r="C148" s="5">
         <v>1.9514100000000001</v>
       </c>
-      <c r="D148" s="4">
+      <c r="D148" s="5">
         <v>-0.59075999999999995</v>
       </c>
-      <c r="E148" s="4">
+      <c r="E148" s="5">
         <v>-0.80286000000000002</v>
       </c>
-      <c r="F148" s="4">
+      <c r="F148" s="5">
         <v>0.40726000000000001</v>
       </c>
-      <c r="G148" s="4">
+      <c r="G148" s="5">
         <v>0.82381000000000004</v>
       </c>
-      <c r="H148" s="6">
+      <c r="H148" s="5">
         <v>-0.86194000000000004</v>
       </c>
-      <c r="I148" s="4">
+      <c r="I148" s="5">
         <v>-0.86648000000000003</v>
       </c>
-      <c r="J148" s="4">
+      <c r="J148" s="5">
         <v>-2.2300000000000002E-3</v>
       </c>
-      <c r="K148" s="4">
+      <c r="K148" s="5">
         <v>1.8903300000000001</v>
       </c>
-      <c r="L148" s="4">
+      <c r="L148" s="5">
         <v>0.10433000000000001</v>
       </c>
-      <c r="M148" s="4">
+      <c r="M148" s="5">
         <v>0.11298</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A149" s="5" t="s">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A149" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B149" s="4">
+      <c r="B149" s="5">
         <v>-1.2353099999999999</v>
       </c>
-      <c r="C149" s="4">
+      <c r="C149" s="5">
         <v>1.33721</v>
       </c>
-      <c r="D149" s="4">
+      <c r="D149" s="5">
         <v>-0.80889</v>
       </c>
-      <c r="E149" s="4">
+      <c r="E149" s="5">
         <v>-1.15143</v>
       </c>
-      <c r="F149" s="4">
+      <c r="F149" s="5">
         <v>0.42758000000000002</v>
       </c>
-      <c r="G149" s="4">
+      <c r="G149" s="5">
         <v>0.65578000000000003</v>
       </c>
-      <c r="H149" s="6">
+      <c r="H149" s="5">
         <v>-1.01468</v>
       </c>
-      <c r="I149" s="4">
+      <c r="I149" s="5">
         <v>-0.43680999999999998</v>
       </c>
-      <c r="J149" s="4">
+      <c r="J149" s="5">
         <v>0.14002000000000001</v>
       </c>
-      <c r="K149" s="4">
+      <c r="K149" s="5">
         <v>1.89595</v>
       </c>
-      <c r="L149" s="4">
+      <c r="L149" s="5">
         <v>0.23089000000000001</v>
       </c>
-      <c r="M149" s="4">
+      <c r="M149" s="5">
         <v>9.0660000000000004E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A150" s="5" t="s">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A150" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="5">
         <v>-0.94255</v>
       </c>
-      <c r="C150" s="4">
+      <c r="C150" s="5">
         <v>1.97116</v>
       </c>
-      <c r="D150" s="4">
+      <c r="D150" s="5">
         <v>-0.58508000000000004</v>
       </c>
-      <c r="E150" s="4">
+      <c r="E150" s="5">
         <v>-1.0865800000000001</v>
       </c>
-      <c r="F150" s="4">
+      <c r="F150" s="5">
         <v>0.47559000000000001</v>
       </c>
-      <c r="G150" s="4">
+      <c r="G150" s="5">
         <v>0.72291000000000005</v>
       </c>
-      <c r="H150" s="6">
+      <c r="H150" s="5">
         <v>-0.83350999999999997</v>
       </c>
-      <c r="I150" s="4">
+      <c r="I150" s="5">
         <v>-1.7947200000000001</v>
       </c>
-      <c r="J150" s="4">
+      <c r="J150" s="5">
         <v>5.8430000000000003E-2</v>
       </c>
-      <c r="K150" s="4">
+      <c r="K150" s="5">
         <v>2.2436199999999999</v>
       </c>
-      <c r="L150" s="4">
+      <c r="L150" s="5">
         <v>-2.5479999999999999E-2</v>
       </c>
-      <c r="M150" s="4">
+      <c r="M150" s="5">
         <v>9.8089999999999997E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="5" t="s">
+    <row r="151" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B151" s="4">
+      <c r="B151" s="5">
         <v>-1.75095</v>
       </c>
-      <c r="C151" s="4">
+      <c r="C151" s="5">
         <v>1.1295999999999999</v>
       </c>
-      <c r="D151" s="4">
+      <c r="D151" s="5">
         <v>-0.31839000000000001</v>
       </c>
-      <c r="E151" s="4">
+      <c r="E151" s="5">
         <v>-0.63078999999999996</v>
       </c>
-      <c r="F151" s="4">
+      <c r="F151" s="5">
         <v>0.41748000000000002</v>
       </c>
-      <c r="G151" s="8">
+      <c r="G151" s="5">
         <v>0.16336999999999999</v>
       </c>
-      <c r="H151" s="4">
+      <c r="H151" s="5">
         <v>-1.67886</v>
       </c>
-      <c r="I151" s="4">
+      <c r="I151" s="5">
         <v>0.57042999999999999</v>
       </c>
-      <c r="J151" s="4">
+      <c r="J151" s="5">
         <v>-0.49434</v>
       </c>
-      <c r="K151" s="4">
+      <c r="K151" s="5">
         <v>1.2363599999999999</v>
       </c>
-      <c r="L151" s="4">
+      <c r="L151" s="5">
         <v>-1.549E-2</v>
       </c>
-      <c r="M151" s="4">
+      <c r="M151" s="5">
         <v>6.0940000000000001E-2</v>
       </c>
-      <c r="N151" s="4"/>
-    </row>
-    <row r="152" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="5" t="s">
+      <c r="N151" s="2"/>
+    </row>
+    <row r="152" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="5">
         <v>-1.6730100000000001</v>
       </c>
-      <c r="C152" s="4">
+      <c r="C152" s="5">
         <v>0.57625999999999999</v>
       </c>
-      <c r="D152" s="4">
+      <c r="D152" s="5">
         <v>4.7919999999999997E-2</v>
       </c>
-      <c r="E152" s="4">
+      <c r="E152" s="5">
         <v>-1.3299799999999999</v>
       </c>
-      <c r="F152" s="4">
+      <c r="F152" s="5">
         <v>0.40705999999999998</v>
       </c>
-      <c r="G152" s="8">
+      <c r="G152" s="5">
         <v>0.68952000000000002</v>
       </c>
-      <c r="H152" s="4">
+      <c r="H152" s="5">
         <v>-1.5515000000000001</v>
       </c>
-      <c r="I152" s="4">
+      <c r="I152" s="5">
         <v>0.44877</v>
       </c>
-      <c r="J152" s="4">
+      <c r="J152" s="5">
         <v>-0.75209999999999999</v>
       </c>
-      <c r="K152" s="4">
+      <c r="K152" s="5">
         <v>1.8655299999999999</v>
       </c>
-      <c r="L152" s="4">
+      <c r="L152" s="5">
         <v>-0.13814000000000001</v>
       </c>
-      <c r="M152" s="4">
+      <c r="M152" s="5">
         <v>-0.21676999999999999</v>
       </c>
-      <c r="N152" s="4"/>
-    </row>
-    <row r="153" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="5" t="s">
+      <c r="N152" s="2"/>
+    </row>
+    <row r="153" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153" s="5">
         <v>-1.7214100000000001</v>
       </c>
-      <c r="C153" s="4">
+      <c r="C153" s="5">
         <v>0.33563999999999999</v>
       </c>
-      <c r="D153" s="4">
+      <c r="D153" s="5">
         <v>-0.24657999999999999</v>
       </c>
-      <c r="E153" s="4">
+      <c r="E153" s="5">
         <v>-1.5463800000000001</v>
       </c>
-      <c r="F153" s="4">
+      <c r="F153" s="5">
         <v>0.19458</v>
       </c>
-      <c r="G153" s="8">
+      <c r="G153" s="5">
         <v>0.51897000000000004</v>
       </c>
-      <c r="H153" s="4">
+      <c r="H153" s="5">
         <v>-1.69547</v>
       </c>
-      <c r="I153" s="4">
+      <c r="I153" s="5">
         <v>0.57084999999999997</v>
       </c>
-      <c r="J153" s="4">
+      <c r="J153" s="5">
         <v>-0.76724000000000003</v>
       </c>
-      <c r="K153" s="4">
+      <c r="K153" s="5">
         <v>2.2573500000000002</v>
       </c>
-      <c r="L153" s="4">
+      <c r="L153" s="5">
         <v>-0.36758000000000002</v>
       </c>
-      <c r="M153" s="4">
+      <c r="M153" s="5">
         <v>-0.23601</v>
       </c>
-      <c r="N153" s="4"/>
-    </row>
-    <row r="154" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="5" t="s">
+      <c r="N153" s="2"/>
+    </row>
+    <row r="154" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="5">
         <v>-1.4542999999999999</v>
       </c>
-      <c r="C154" s="4">
+      <c r="C154" s="5">
         <v>1.8724400000000001</v>
       </c>
-      <c r="D154" s="4">
+      <c r="D154" s="5">
         <v>0.65219000000000005</v>
       </c>
-      <c r="E154" s="4">
+      <c r="E154" s="5">
         <v>-0.77830999999999995</v>
       </c>
-      <c r="F154" s="4">
+      <c r="F154" s="5">
         <v>0.58396000000000003</v>
       </c>
-      <c r="G154" s="8">
+      <c r="G154" s="5">
         <v>0.91164999999999996</v>
       </c>
-      <c r="H154" s="4">
+      <c r="H154" s="5">
         <v>-1.5523899999999999</v>
       </c>
-      <c r="I154" s="4">
+      <c r="I154" s="5">
         <v>0.36637999999999998</v>
       </c>
-      <c r="J154" s="4">
+      <c r="J154" s="5">
         <v>-0.39689000000000002</v>
       </c>
-      <c r="K154" s="4">
+      <c r="K154" s="5">
         <v>1.44339</v>
       </c>
-      <c r="L154" s="4">
+      <c r="L154" s="5">
         <v>-4.5850000000000002E-2</v>
       </c>
-      <c r="M154" s="4">
+      <c r="M154" s="5">
         <v>-0.10534</v>
       </c>
-      <c r="N154" s="4"/>
-    </row>
-    <row r="155" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="5" t="s">
+      <c r="N154" s="2"/>
+    </row>
+    <row r="155" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B155" s="4">
+      <c r="B155" s="5">
         <v>-1.41262</v>
       </c>
-      <c r="C155" s="4">
+      <c r="C155" s="5">
         <v>1.13812</v>
       </c>
-      <c r="D155" s="4">
+      <c r="D155" s="5">
         <v>0.37431999999999999</v>
       </c>
-      <c r="E155" s="4">
+      <c r="E155" s="5">
         <v>-0.98475000000000001</v>
       </c>
-      <c r="F155" s="4">
+      <c r="F155" s="5">
         <v>0.46444000000000002</v>
       </c>
-      <c r="G155" s="8">
+      <c r="G155" s="5">
         <v>1.2065300000000001</v>
       </c>
-      <c r="H155" s="4">
+      <c r="H155" s="5">
         <v>-1.49885</v>
       </c>
-      <c r="I155" s="4">
+      <c r="I155" s="5">
         <v>0.55715000000000003</v>
       </c>
-      <c r="J155" s="4">
+      <c r="J155" s="5">
         <v>-0.64786999999999995</v>
       </c>
-      <c r="K155" s="4">
+      <c r="K155" s="5">
         <v>2.2547100000000002</v>
       </c>
-      <c r="L155" s="4">
+      <c r="L155" s="5">
         <v>-3.8859999999999999E-2</v>
       </c>
-      <c r="M155" s="4">
+      <c r="M155" s="5">
         <v>-0.10077</v>
       </c>
-      <c r="N155" s="4"/>
+      <c r="N155" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
